--- a/research/traditional_assets/database/data/vietnam/vietnam_auto_parts.xlsx
+++ b/research/traditional_assets/database/data/vietnam/vietnam_auto_parts.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.145215074901648</v>
+        <v>0.1449606447518447</v>
       </c>
       <c r="C2">
-        <v>128.6486398994695</v>
+        <v>127.6877206385044</v>
       </c>
       <c r="D2">
-        <v>122.4086398994695</v>
+        <v>122.7227206385044</v>
       </c>
       <c r="E2">
-        <v>-50.1</v>
+        <v>-48.825</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.275</v>
       </c>
       <c r="G2">
         <v>6.24</v>
@@ -1451,28 +1451,28 @@
         <v>9.885</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.06413250000000001</v>
       </c>
       <c r="N2">
-        <v>9.885</v>
+        <v>9.8208675</v>
       </c>
       <c r="O2">
-        <v>1.977</v>
+        <v>1.9641735</v>
       </c>
       <c r="P2">
-        <v>7.907999999999999</v>
+        <v>7.856694</v>
       </c>
       <c r="Q2">
-        <v>11.148</v>
+        <v>11.096694</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.145215074901648</v>
+        <v>0.1460184290422674</v>
       </c>
       <c r="T2">
-        <v>1.190966980496056</v>
+        <v>1.200590956096024</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>154.1340194129342</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1449606447518447</v>
+        <v>0.1447062146020414</v>
       </c>
       <c r="C3">
-        <v>127.6877206385044</v>
+        <v>126.728417284281</v>
       </c>
       <c r="D3">
-        <v>122.7227206385044</v>
+        <v>123.038417284281</v>
       </c>
       <c r="E3">
-        <v>-48.825</v>
+        <v>-47.55</v>
       </c>
       <c r="F3">
-        <v>1.275</v>
+        <v>2.55</v>
       </c>
       <c r="G3">
         <v>6.24</v>
@@ -1533,28 +1533,28 @@
         <v>9.885</v>
       </c>
       <c r="M3">
-        <v>0.06413250000000001</v>
+        <v>0.128265</v>
       </c>
       <c r="N3">
-        <v>9.8208675</v>
+        <v>9.756734999999999</v>
       </c>
       <c r="O3">
-        <v>1.9641735</v>
+        <v>1.951347</v>
       </c>
       <c r="P3">
-        <v>7.856694</v>
+        <v>7.805387999999999</v>
       </c>
       <c r="Q3">
-        <v>11.096694</v>
+        <v>11.045388</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1460184290422674</v>
+        <v>0.1468381781653484</v>
       </c>
       <c r="T3">
-        <v>1.200590956096024</v>
+        <v>1.210411339361297</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>154.1340194129342</v>
+        <v>77.06700970646706</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1447062146020414</v>
+        <v>0.1444517844522381</v>
       </c>
       <c r="C4">
-        <v>126.728417284281</v>
+        <v>125.7707423394234</v>
       </c>
       <c r="D4">
-        <v>123.038417284281</v>
+        <v>123.3557423394234</v>
       </c>
       <c r="E4">
-        <v>-47.55</v>
+        <v>-46.275</v>
       </c>
       <c r="F4">
-        <v>2.55</v>
+        <v>3.825</v>
       </c>
       <c r="G4">
         <v>6.24</v>
@@ -1615,28 +1615,28 @@
         <v>9.885</v>
       </c>
       <c r="M4">
-        <v>0.128265</v>
+        <v>0.1923975</v>
       </c>
       <c r="N4">
-        <v>9.756734999999999</v>
+        <v>9.6926025</v>
       </c>
       <c r="O4">
-        <v>1.951347</v>
+        <v>1.9385205</v>
       </c>
       <c r="P4">
-        <v>7.805387999999999</v>
+        <v>7.754081999999999</v>
       </c>
       <c r="Q4">
-        <v>11.045388</v>
+        <v>10.994082</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1468381781653484</v>
+        <v>0.1476748293322042</v>
       </c>
       <c r="T4">
-        <v>1.210411339361297</v>
+        <v>1.220434204755752</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>77.06700970646706</v>
+        <v>51.37800647097806</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1444517844522381</v>
+        <v>0.1441973543024348</v>
       </c>
       <c r="C5">
-        <v>125.7707423394234</v>
+        <v>124.81470843587</v>
       </c>
       <c r="D5">
-        <v>123.3557423394234</v>
+        <v>123.67470843587</v>
       </c>
       <c r="E5">
-        <v>-46.275</v>
+        <v>-45</v>
       </c>
       <c r="F5">
-        <v>3.825</v>
+        <v>5.100000000000001</v>
       </c>
       <c r="G5">
         <v>6.24</v>
@@ -1697,28 +1697,28 @@
         <v>9.885</v>
       </c>
       <c r="M5">
-        <v>0.1923975</v>
+        <v>0.25653</v>
       </c>
       <c r="N5">
-        <v>9.6926025</v>
+        <v>9.62847</v>
       </c>
       <c r="O5">
-        <v>1.9385205</v>
+        <v>1.925694</v>
       </c>
       <c r="P5">
-        <v>7.754081999999999</v>
+        <v>7.702776</v>
       </c>
       <c r="Q5">
-        <v>10.994082</v>
+        <v>10.942776</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1476748293322042</v>
+        <v>0.1485289107317029</v>
       </c>
       <c r="T5">
-        <v>1.220434204755752</v>
+        <v>1.230665879845924</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>51.37800647097806</v>
+        <v>38.53350485323354</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1441973543024348</v>
+        <v>0.1439429241526315</v>
       </c>
       <c r="C6">
-        <v>124.81470843587</v>
+        <v>123.8603283365496</v>
       </c>
       <c r="D6">
-        <v>123.67470843587</v>
+        <v>123.9953283365496</v>
       </c>
       <c r="E6">
-        <v>-45</v>
+        <v>-43.725</v>
       </c>
       <c r="F6">
-        <v>5.100000000000001</v>
+        <v>6.375</v>
       </c>
       <c r="G6">
         <v>6.24</v>
@@ -1779,28 +1779,28 @@
         <v>9.885</v>
       </c>
       <c r="M6">
-        <v>0.25653</v>
+        <v>0.3206625</v>
       </c>
       <c r="N6">
-        <v>9.62847</v>
+        <v>9.564337500000001</v>
       </c>
       <c r="O6">
-        <v>1.925694</v>
+        <v>1.9128675</v>
       </c>
       <c r="P6">
-        <v>7.702776</v>
+        <v>7.651470000000001</v>
       </c>
       <c r="Q6">
-        <v>10.942776</v>
+        <v>10.89147</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1485289107317029</v>
+        <v>0.1494009727922437</v>
       </c>
       <c r="T6">
-        <v>1.230665879845924</v>
+        <v>1.241112958622205</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>38.53350485323354</v>
+        <v>30.82680388258684</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1439429241526315</v>
+        <v>0.1436884940028283</v>
       </c>
       <c r="C7">
-        <v>123.8603283365496</v>
+        <v>122.9076149370836</v>
       </c>
       <c r="D7">
-        <v>123.9953283365496</v>
+        <v>124.3176149370836</v>
       </c>
       <c r="E7">
-        <v>-43.725</v>
+        <v>-42.45</v>
       </c>
       <c r="F7">
-        <v>6.375</v>
+        <v>7.65</v>
       </c>
       <c r="G7">
         <v>6.24</v>
@@ -1861,28 +1861,28 @@
         <v>9.885</v>
       </c>
       <c r="M7">
-        <v>0.3206625</v>
+        <v>0.384795</v>
       </c>
       <c r="N7">
-        <v>9.564337500000001</v>
+        <v>9.500204999999999</v>
       </c>
       <c r="O7">
-        <v>1.9128675</v>
+        <v>1.900041</v>
       </c>
       <c r="P7">
-        <v>7.651470000000001</v>
+        <v>7.600163999999999</v>
       </c>
       <c r="Q7">
-        <v>10.89147</v>
+        <v>10.840164</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1494009727922437</v>
+        <v>0.1502915893647109</v>
       </c>
       <c r="T7">
-        <v>1.241112958622205</v>
+        <v>1.251782315670322</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>30.82680388258684</v>
+        <v>25.68900323548903</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1436884940028283</v>
+        <v>0.143434063853025</v>
       </c>
       <c r="C8">
-        <v>122.9076149370836</v>
+        <v>121.9565812675156</v>
       </c>
       <c r="D8">
-        <v>124.3176149370836</v>
+        <v>124.6415812675156</v>
       </c>
       <c r="E8">
-        <v>-42.45</v>
+        <v>-41.175</v>
       </c>
       <c r="F8">
-        <v>7.649999999999999</v>
+        <v>8.924999999999999</v>
       </c>
       <c r="G8">
         <v>6.24</v>
@@ -1943,28 +1943,28 @@
         <v>9.885</v>
       </c>
       <c r="M8">
-        <v>0.3847949999999999</v>
+        <v>0.4489274999999999</v>
       </c>
       <c r="N8">
-        <v>9.500204999999999</v>
+        <v>9.4360725</v>
       </c>
       <c r="O8">
-        <v>1.900041</v>
+        <v>1.8872145</v>
       </c>
       <c r="P8">
-        <v>7.600163999999999</v>
+        <v>7.548858</v>
       </c>
       <c r="Q8">
-        <v>10.840164</v>
+        <v>10.788858</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1502915893647109</v>
+        <v>0.1512013589817472</v>
       </c>
       <c r="T8">
-        <v>1.251782315670322</v>
+        <v>1.262681121257109</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>25.68900323548903</v>
+        <v>22.01914563041917</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1434340638530249</v>
+        <v>0.1431796337032216</v>
       </c>
       <c r="C9">
-        <v>121.9565812675157</v>
+        <v>121.0072404940667</v>
       </c>
       <c r="D9">
-        <v>124.6415812675157</v>
+        <v>124.9672404940667</v>
       </c>
       <c r="E9">
-        <v>-41.175</v>
+        <v>-39.9</v>
       </c>
       <c r="F9">
-        <v>8.925000000000001</v>
+        <v>10.2</v>
       </c>
       <c r="G9">
         <v>6.24</v>
@@ -2025,28 +2025,28 @@
         <v>9.885</v>
       </c>
       <c r="M9">
-        <v>0.4489275</v>
+        <v>0.5130600000000001</v>
       </c>
       <c r="N9">
-        <v>9.4360725</v>
+        <v>9.37194</v>
       </c>
       <c r="O9">
-        <v>1.8872145</v>
+        <v>1.874388</v>
       </c>
       <c r="P9">
-        <v>7.548858</v>
+        <v>7.497552000000001</v>
       </c>
       <c r="Q9">
-        <v>10.788858</v>
+        <v>10.737552</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1512013589817472</v>
+        <v>0.152130906199154</v>
       </c>
       <c r="T9">
-        <v>1.262681121257109</v>
+        <v>1.273816857400129</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>22.01914563041916</v>
+        <v>19.26675242661677</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1431796337032216</v>
+        <v>0.1429252035534183</v>
       </c>
       <c r="C10">
-        <v>121.0072404940667</v>
+        <v>120.0596059209193</v>
       </c>
       <c r="D10">
-        <v>124.9672404940667</v>
+        <v>125.2946059209193</v>
       </c>
       <c r="E10">
-        <v>-39.9</v>
+        <v>-38.625</v>
       </c>
       <c r="F10">
-        <v>10.2</v>
+        <v>11.475</v>
       </c>
       <c r="G10">
         <v>6.24</v>
@@ -2107,28 +2107,28 @@
         <v>9.885</v>
       </c>
       <c r="M10">
-        <v>0.5130600000000001</v>
+        <v>0.5771925</v>
       </c>
       <c r="N10">
-        <v>9.37194</v>
+        <v>9.307807499999999</v>
       </c>
       <c r="O10">
-        <v>1.874388</v>
+        <v>1.8615615</v>
       </c>
       <c r="P10">
-        <v>7.497552000000001</v>
+        <v>7.446245999999999</v>
       </c>
       <c r="Q10">
-        <v>10.737552</v>
+        <v>10.686246</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.152130906199154</v>
+        <v>0.1530808830257344</v>
       </c>
       <c r="T10">
-        <v>1.273816857400129</v>
+        <v>1.285197334996842</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>19.26675242661677</v>
+        <v>17.12600215699268</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1429252035534183</v>
+        <v>0.1426707734036151</v>
       </c>
       <c r="C11">
-        <v>120.0596059209193</v>
+        <v>119.1136909920292</v>
       </c>
       <c r="D11">
-        <v>125.2946059209193</v>
+        <v>125.6236909920292</v>
       </c>
       <c r="E11">
-        <v>-38.625</v>
+        <v>-37.35</v>
       </c>
       <c r="F11">
-        <v>11.475</v>
+        <v>12.75</v>
       </c>
       <c r="G11">
         <v>6.24</v>
@@ -2189,28 +2189,28 @@
         <v>9.885</v>
       </c>
       <c r="M11">
-        <v>0.5771925</v>
+        <v>0.6413249999999999</v>
       </c>
       <c r="N11">
-        <v>9.307807499999999</v>
+        <v>9.243675</v>
       </c>
       <c r="O11">
-        <v>1.8615615</v>
+        <v>1.848735</v>
       </c>
       <c r="P11">
-        <v>7.446245999999999</v>
+        <v>7.39494</v>
       </c>
       <c r="Q11">
-        <v>10.686246</v>
+        <v>10.63494</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1530808830257344</v>
+        <v>0.1540519704484612</v>
       </c>
       <c r="T11">
-        <v>1.285197334996842</v>
+        <v>1.296830712095705</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>17.12600215699268</v>
+        <v>15.41340194129342</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1426707734036151</v>
+        <v>0.1424163432538118</v>
       </c>
       <c r="C12">
-        <v>119.1136909920292</v>
+        <v>118.169509292966</v>
       </c>
       <c r="D12">
-        <v>125.6236909920292</v>
+        <v>125.954509292966</v>
       </c>
       <c r="E12">
-        <v>-37.35</v>
+        <v>-36.075</v>
       </c>
       <c r="F12">
-        <v>12.75</v>
+        <v>14.025</v>
       </c>
       <c r="G12">
         <v>6.24</v>
@@ -2271,28 +2271,28 @@
         <v>9.885</v>
       </c>
       <c r="M12">
-        <v>0.6413249999999999</v>
+        <v>0.7054575</v>
       </c>
       <c r="N12">
-        <v>9.243675</v>
+        <v>9.1795425</v>
       </c>
       <c r="O12">
-        <v>1.848735</v>
+        <v>1.8359085</v>
       </c>
       <c r="P12">
-        <v>7.39494</v>
+        <v>7.343634</v>
       </c>
       <c r="Q12">
-        <v>10.63494</v>
+        <v>10.583634</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1540519704484612</v>
+        <v>0.1550448800604626</v>
       </c>
       <c r="T12">
-        <v>1.296830712095705</v>
+        <v>1.308725513399036</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>15.41340194129342</v>
+        <v>14.01218358299402</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1424163432538118</v>
+        <v>0.1423059131040084</v>
       </c>
       <c r="C13">
-        <v>118.169509292966</v>
+        <v>117.038636993355</v>
       </c>
       <c r="D13">
-        <v>125.954509292966</v>
+        <v>126.098636993355</v>
       </c>
       <c r="E13">
-        <v>-36.075</v>
+        <v>-34.8</v>
       </c>
       <c r="F13">
-        <v>14.025</v>
+        <v>15.3</v>
       </c>
       <c r="G13">
         <v>6.24</v>
@@ -2353,45 +2353,45 @@
         <v>9.885</v>
       </c>
       <c r="M13">
-        <v>0.7054575</v>
+        <v>0.7925399999999999</v>
       </c>
       <c r="N13">
-        <v>9.1795425</v>
+        <v>9.092459999999999</v>
       </c>
       <c r="O13">
-        <v>1.8359085</v>
+        <v>1.818492</v>
       </c>
       <c r="P13">
-        <v>7.343634</v>
+        <v>7.273967999999999</v>
       </c>
       <c r="Q13">
-        <v>10.583634</v>
+        <v>10.513968</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1550448800604626</v>
+        <v>0.1560603558000096</v>
       </c>
       <c r="T13">
-        <v>1.308725513399036</v>
+        <v>1.320890651095625</v>
       </c>
       <c r="U13">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V13">
         <v>0.2</v>
       </c>
       <c r="W13">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>14.01218358299402</v>
+        <v>12.47255659020365</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1423059131040084</v>
+        <v>0.1420634829542052</v>
       </c>
       <c r="C14">
-        <v>117.038636993355</v>
+        <v>116.08120405532</v>
       </c>
       <c r="D14">
-        <v>126.098636993355</v>
+        <v>126.41620405532</v>
       </c>
       <c r="E14">
-        <v>-34.8</v>
+        <v>-33.52500000000001</v>
       </c>
       <c r="F14">
-        <v>15.3</v>
+        <v>16.575</v>
       </c>
       <c r="G14">
         <v>6.24</v>
@@ -2435,28 +2435,28 @@
         <v>9.885</v>
       </c>
       <c r="M14">
-        <v>0.7925399999999999</v>
+        <v>0.8585849999999999</v>
       </c>
       <c r="N14">
-        <v>9.092459999999999</v>
+        <v>9.026415</v>
       </c>
       <c r="O14">
-        <v>1.818492</v>
+        <v>1.805283</v>
       </c>
       <c r="P14">
-        <v>7.273967999999999</v>
+        <v>7.221132</v>
       </c>
       <c r="Q14">
-        <v>10.513968</v>
+        <v>10.461132</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1560603558000096</v>
+        <v>0.1570991758094312</v>
       </c>
       <c r="T14">
-        <v>1.320890651095625</v>
+        <v>1.333335447130067</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>12.47255659020365</v>
+        <v>11.51312916018798</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1420634829542052</v>
+        <v>0.1418210528044019</v>
       </c>
       <c r="C15">
-        <v>116.08120405532</v>
+        <v>115.1253746787574</v>
       </c>
       <c r="D15">
-        <v>126.41620405532</v>
+        <v>126.7353746787574</v>
       </c>
       <c r="E15">
-        <v>-33.52500000000001</v>
+        <v>-32.25</v>
       </c>
       <c r="F15">
-        <v>16.575</v>
+        <v>17.85</v>
       </c>
       <c r="G15">
         <v>6.24</v>
@@ -2517,28 +2517,28 @@
         <v>9.885</v>
       </c>
       <c r="M15">
-        <v>0.8585849999999999</v>
+        <v>0.9246300000000001</v>
       </c>
       <c r="N15">
-        <v>9.026415</v>
+        <v>8.960369999999999</v>
       </c>
       <c r="O15">
-        <v>1.805283</v>
+        <v>1.792074</v>
       </c>
       <c r="P15">
-        <v>7.221132</v>
+        <v>7.168296</v>
       </c>
       <c r="Q15">
-        <v>10.461132</v>
+        <v>10.408296</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1570991758094312</v>
+        <v>0.1581621544237231</v>
       </c>
       <c r="T15">
-        <v>1.333335447130067</v>
+        <v>1.346069657025775</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.51312916018798</v>
+        <v>10.69076279160313</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1418210528044019</v>
+        <v>0.1415786226545986</v>
       </c>
       <c r="C16">
-        <v>115.1253746787574</v>
+        <v>114.1711610402355</v>
       </c>
       <c r="D16">
-        <v>126.7353746787574</v>
+        <v>127.0561610402355</v>
       </c>
       <c r="E16">
-        <v>-32.25</v>
+        <v>-30.975</v>
       </c>
       <c r="F16">
-        <v>17.85</v>
+        <v>19.125</v>
       </c>
       <c r="G16">
         <v>6.24</v>
@@ -2599,28 +2599,28 @@
         <v>9.885</v>
       </c>
       <c r="M16">
-        <v>0.9246300000000001</v>
+        <v>0.9906750000000002</v>
       </c>
       <c r="N16">
-        <v>8.960369999999999</v>
+        <v>8.894325</v>
       </c>
       <c r="O16">
-        <v>1.792074</v>
+        <v>1.778865</v>
       </c>
       <c r="P16">
-        <v>7.168296</v>
+        <v>7.115460000000001</v>
       </c>
       <c r="Q16">
-        <v>10.408296</v>
+        <v>10.35546</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1581621544237231</v>
+        <v>0.1592501442995277</v>
       </c>
       <c r="T16">
-        <v>1.346069657025775</v>
+        <v>1.359103495389616</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>10.69076279160313</v>
+        <v>9.978045272162918</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1415786226545986</v>
+        <v>0.1415537925047952</v>
       </c>
       <c r="C17">
-        <v>114.1711610402355</v>
+        <v>112.9291082836766</v>
       </c>
       <c r="D17">
-        <v>127.0561610402355</v>
+        <v>127.0891082836766</v>
       </c>
       <c r="E17">
-        <v>-30.975</v>
+        <v>-29.7</v>
       </c>
       <c r="F17">
-        <v>19.125</v>
+        <v>20.4</v>
       </c>
       <c r="G17">
         <v>6.24</v>
@@ -2681,45 +2681,45 @@
         <v>9.885</v>
       </c>
       <c r="M17">
-        <v>0.990675</v>
+        <v>1.0914</v>
       </c>
       <c r="N17">
-        <v>8.894325</v>
+        <v>8.7936</v>
       </c>
       <c r="O17">
-        <v>1.778865</v>
+        <v>1.75872</v>
       </c>
       <c r="P17">
-        <v>7.115460000000001</v>
+        <v>7.034879999999999</v>
       </c>
       <c r="Q17">
-        <v>10.35546</v>
+        <v>10.27488</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1592501442995277</v>
+        <v>0.1603640386961848</v>
       </c>
       <c r="T17">
-        <v>1.359103495389616</v>
+        <v>1.372447663238312</v>
       </c>
       <c r="U17">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V17">
         <v>0.2</v>
       </c>
       <c r="W17">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y17">
-        <v>9.97804527216292</v>
+        <v>9.057174271577789</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1415537925047952</v>
+        <v>0.141324962354992</v>
       </c>
       <c r="C18">
-        <v>112.9291082836766</v>
+        <v>111.9585503789149</v>
       </c>
       <c r="D18">
-        <v>127.0891082836766</v>
+        <v>127.3935503789149</v>
       </c>
       <c r="E18">
-        <v>-29.7</v>
+        <v>-28.425</v>
       </c>
       <c r="F18">
-        <v>20.4</v>
+        <v>21.675</v>
       </c>
       <c r="G18">
         <v>6.24</v>
@@ -2763,28 +2763,28 @@
         <v>9.885</v>
       </c>
       <c r="M18">
-        <v>1.0914</v>
+        <v>1.1596125</v>
       </c>
       <c r="N18">
-        <v>8.7936</v>
+        <v>8.7253875</v>
       </c>
       <c r="O18">
-        <v>1.75872</v>
+        <v>1.7450775</v>
       </c>
       <c r="P18">
-        <v>7.034879999999999</v>
+        <v>6.98031</v>
       </c>
       <c r="Q18">
-        <v>10.27488</v>
+        <v>10.22031</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1603640386961848</v>
+        <v>0.1615047739216771</v>
       </c>
       <c r="T18">
-        <v>1.372447663238312</v>
+        <v>1.386113377300229</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>9.057174271577789</v>
+        <v>8.524399314426155</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.141324962354992</v>
+        <v>0.1410961322051887</v>
       </c>
       <c r="C19">
-        <v>111.9585503789149</v>
+        <v>110.9894545593114</v>
       </c>
       <c r="D19">
-        <v>127.3935503789149</v>
+        <v>127.6994545593114</v>
       </c>
       <c r="E19">
-        <v>-28.425</v>
+        <v>-27.15</v>
       </c>
       <c r="F19">
-        <v>21.675</v>
+        <v>22.95</v>
       </c>
       <c r="G19">
         <v>6.24</v>
@@ -2845,28 +2845,28 @@
         <v>9.885</v>
       </c>
       <c r="M19">
-        <v>1.1596125</v>
+        <v>1.227825</v>
       </c>
       <c r="N19">
-        <v>8.7253875</v>
+        <v>8.657174999999999</v>
       </c>
       <c r="O19">
-        <v>1.7450775</v>
+        <v>1.731435</v>
       </c>
       <c r="P19">
-        <v>6.98031</v>
+        <v>6.925739999999999</v>
       </c>
       <c r="Q19">
-        <v>10.22031</v>
+        <v>10.16574</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1615047739216771</v>
+        <v>0.1626733319575472</v>
       </c>
       <c r="T19">
-        <v>1.386113377300229</v>
+        <v>1.400112401461217</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.524399314426155</v>
+        <v>8.05082157473581</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1410961322051887</v>
+        <v>0.1408673020553854</v>
       </c>
       <c r="C20">
-        <v>110.9894545593114</v>
+        <v>110.0218313827284</v>
       </c>
       <c r="D20">
-        <v>127.6994545593114</v>
+        <v>128.0068313827283</v>
       </c>
       <c r="E20">
-        <v>-27.15</v>
+        <v>-25.875</v>
       </c>
       <c r="F20">
-        <v>22.95</v>
+        <v>24.225</v>
       </c>
       <c r="G20">
         <v>6.24</v>
@@ -2927,28 +2927,28 @@
         <v>9.885</v>
       </c>
       <c r="M20">
-        <v>1.227825</v>
+        <v>1.2960375</v>
       </c>
       <c r="N20">
-        <v>8.657175000000001</v>
+        <v>8.588962499999999</v>
       </c>
       <c r="O20">
-        <v>1.731435</v>
+        <v>1.7177925</v>
       </c>
       <c r="P20">
-        <v>6.92574</v>
+        <v>6.871169999999999</v>
       </c>
       <c r="Q20">
-        <v>10.16574</v>
+        <v>10.11117</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1626733319575472</v>
+        <v>0.1638707432782536</v>
       </c>
       <c r="T20">
-        <v>1.400112401461217</v>
+        <v>1.41445708053976</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.050821574735814</v>
+        <v>7.627094123433928</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1408673020553854</v>
+        <v>0.1407664719055821</v>
       </c>
       <c r="C21">
-        <v>110.0218313827284</v>
+        <v>108.8827419596423</v>
       </c>
       <c r="D21">
-        <v>128.0068313827283</v>
+        <v>128.1427419596423</v>
       </c>
       <c r="E21">
-        <v>-25.875</v>
+        <v>-24.6</v>
       </c>
       <c r="F21">
-        <v>24.225</v>
+        <v>25.5</v>
       </c>
       <c r="G21">
         <v>6.24</v>
@@ -3009,45 +3009,45 @@
         <v>9.885</v>
       </c>
       <c r="M21">
-        <v>1.2960375</v>
+        <v>1.38465</v>
       </c>
       <c r="N21">
-        <v>8.588962499999999</v>
+        <v>8.500349999999999</v>
       </c>
       <c r="O21">
-        <v>1.7177925</v>
+        <v>1.70007</v>
       </c>
       <c r="P21">
-        <v>6.871169999999999</v>
+        <v>6.800279999999999</v>
       </c>
       <c r="Q21">
-        <v>10.11117</v>
+        <v>10.04028</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1638707432782536</v>
+        <v>0.1650980898819776</v>
       </c>
       <c r="T21">
-        <v>1.41445708053976</v>
+        <v>1.429160376595267</v>
       </c>
       <c r="U21">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V21">
         <v>0.2</v>
       </c>
       <c r="W21">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y21">
-        <v>7.627094123433928</v>
+        <v>7.138988191961867</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1407664719055821</v>
+        <v>0.1405440417557788</v>
       </c>
       <c r="C22">
-        <v>108.8827419596423</v>
+        <v>107.9085820838557</v>
       </c>
       <c r="D22">
-        <v>128.1427419596423</v>
+        <v>128.4435820838557</v>
       </c>
       <c r="E22">
-        <v>-24.6</v>
+        <v>-23.325</v>
       </c>
       <c r="F22">
-        <v>25.5</v>
+        <v>26.775</v>
       </c>
       <c r="G22">
         <v>6.24</v>
@@ -3091,28 +3091,28 @@
         <v>9.885</v>
       </c>
       <c r="M22">
-        <v>1.38465</v>
+        <v>1.4538825</v>
       </c>
       <c r="N22">
-        <v>8.500349999999999</v>
+        <v>8.431117499999999</v>
       </c>
       <c r="O22">
-        <v>1.70007</v>
+        <v>1.6862235</v>
       </c>
       <c r="P22">
-        <v>6.800279999999999</v>
+        <v>6.744894</v>
       </c>
       <c r="Q22">
-        <v>10.04028</v>
+        <v>9.984894000000001</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1650980898819776</v>
+        <v>0.1663565085516187</v>
       </c>
       <c r="T22">
-        <v>1.429160376595267</v>
+        <v>1.444235907993951</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>7.138988191961867</v>
+        <v>6.799036373297016</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1405440417557788</v>
+        <v>0.1403216116059755</v>
       </c>
       <c r="C23">
-        <v>107.9085820838557</v>
+        <v>106.935838094082</v>
       </c>
       <c r="D23">
-        <v>128.4435820838557</v>
+        <v>128.745838094082</v>
       </c>
       <c r="E23">
-        <v>-23.325</v>
+        <v>-22.05</v>
       </c>
       <c r="F23">
-        <v>26.775</v>
+        <v>28.05</v>
       </c>
       <c r="G23">
         <v>6.24</v>
@@ -3173,28 +3173,28 @@
         <v>9.885</v>
       </c>
       <c r="M23">
-        <v>1.4538825</v>
+        <v>1.523115</v>
       </c>
       <c r="N23">
-        <v>8.431117499999999</v>
+        <v>8.361884999999999</v>
       </c>
       <c r="O23">
-        <v>1.6862235</v>
+        <v>1.672377</v>
       </c>
       <c r="P23">
-        <v>6.744894</v>
+        <v>6.689507999999999</v>
       </c>
       <c r="Q23">
-        <v>9.984894000000001</v>
+        <v>9.929507999999998</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1663565085516187</v>
+        <v>0.1676471943666352</v>
       </c>
       <c r="T23">
-        <v>1.444235907993951</v>
+        <v>1.459697991479781</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.799036373297016</v>
+        <v>6.489989265419879</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1403216116059755</v>
+        <v>0.1400991814561722</v>
       </c>
       <c r="C24">
-        <v>106.935838094082</v>
+        <v>105.9645200095727</v>
       </c>
       <c r="D24">
-        <v>128.745838094082</v>
+        <v>129.0495200095727</v>
       </c>
       <c r="E24">
-        <v>-22.05</v>
+        <v>-20.775</v>
       </c>
       <c r="F24">
-        <v>28.05</v>
+        <v>29.325</v>
       </c>
       <c r="G24">
         <v>6.24</v>
@@ -3255,28 +3255,28 @@
         <v>9.885</v>
       </c>
       <c r="M24">
-        <v>1.523115</v>
+        <v>1.5923475</v>
       </c>
       <c r="N24">
-        <v>8.361884999999999</v>
+        <v>8.292652499999999</v>
       </c>
       <c r="O24">
-        <v>1.672377</v>
+        <v>1.6585305</v>
       </c>
       <c r="P24">
-        <v>6.689507999999999</v>
+        <v>6.634122</v>
       </c>
       <c r="Q24">
-        <v>9.929507999999998</v>
+        <v>9.874122</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1676471943666352</v>
+        <v>0.1689714044885353</v>
       </c>
       <c r="T24">
-        <v>1.459697991479781</v>
+        <v>1.475561687523685</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.489989265419879</v>
+        <v>6.207815819097275</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1400991814561722</v>
+        <v>0.1400687513063689</v>
       </c>
       <c r="C25">
-        <v>105.9645200095727</v>
+        <v>104.7311774641535</v>
       </c>
       <c r="D25">
-        <v>129.0495200095727</v>
+        <v>129.0911774641535</v>
       </c>
       <c r="E25">
-        <v>-20.775</v>
+        <v>-19.5</v>
       </c>
       <c r="F25">
-        <v>29.325</v>
+        <v>30.6</v>
       </c>
       <c r="G25">
         <v>6.24</v>
@@ -3337,45 +3337,45 @@
         <v>9.885</v>
       </c>
       <c r="M25">
-        <v>1.5923475</v>
+        <v>1.69218</v>
       </c>
       <c r="N25">
-        <v>8.292652499999999</v>
+        <v>8.192819999999999</v>
       </c>
       <c r="O25">
-        <v>1.6585305</v>
+        <v>1.638564</v>
       </c>
       <c r="P25">
-        <v>6.634122</v>
+        <v>6.554256</v>
       </c>
       <c r="Q25">
-        <v>9.874122</v>
+        <v>9.794256000000001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1689714044885353</v>
+        <v>0.1703304622452222</v>
       </c>
       <c r="T25">
-        <v>1.475561687523685</v>
+        <v>1.491842849252954</v>
       </c>
       <c r="U25">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V25">
         <v>0.2</v>
       </c>
       <c r="W25">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y25">
-        <v>6.207815819097275</v>
+        <v>5.841577137183987</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1400687513063689</v>
+        <v>0.1398543211565656</v>
       </c>
       <c r="C26">
-        <v>104.7311774641535</v>
+        <v>103.7504865419453</v>
       </c>
       <c r="D26">
-        <v>129.0911774641535</v>
+        <v>129.3854865419453</v>
       </c>
       <c r="E26">
-        <v>-19.5</v>
+        <v>-18.225</v>
       </c>
       <c r="F26">
-        <v>30.6</v>
+        <v>31.875</v>
       </c>
       <c r="G26">
         <v>6.24</v>
@@ -3419,28 +3419,28 @@
         <v>9.885</v>
       </c>
       <c r="M26">
-        <v>1.69218</v>
+        <v>1.7626875</v>
       </c>
       <c r="N26">
-        <v>8.192819999999999</v>
+        <v>8.1223125</v>
       </c>
       <c r="O26">
-        <v>1.638564</v>
+        <v>1.6244625</v>
       </c>
       <c r="P26">
-        <v>6.554256</v>
+        <v>6.49785</v>
       </c>
       <c r="Q26">
-        <v>9.794256000000001</v>
+        <v>9.73785</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1703304622452222</v>
+        <v>0.1717257615420875</v>
       </c>
       <c r="T26">
-        <v>1.491842849252954</v>
+        <v>1.508558175295004</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.841577137183987</v>
+        <v>5.607914051696627</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1398543211565656</v>
+        <v>0.1396398910067623</v>
       </c>
       <c r="C27">
-        <v>103.7504865419453</v>
+        <v>102.7711406498509</v>
       </c>
       <c r="D27">
-        <v>129.3854865419453</v>
+        <v>129.6811406498509</v>
       </c>
       <c r="E27">
-        <v>-18.225</v>
+        <v>-16.95</v>
       </c>
       <c r="F27">
-        <v>31.875</v>
+        <v>33.15</v>
       </c>
       <c r="G27">
         <v>6.24</v>
@@ -3501,28 +3501,28 @@
         <v>9.885</v>
       </c>
       <c r="M27">
-        <v>1.7626875</v>
+        <v>1.833195</v>
       </c>
       <c r="N27">
-        <v>8.1223125</v>
+        <v>8.051805</v>
       </c>
       <c r="O27">
-        <v>1.6244625</v>
+        <v>1.610361</v>
       </c>
       <c r="P27">
-        <v>6.49785</v>
+        <v>6.441444</v>
       </c>
       <c r="Q27">
-        <v>9.73785</v>
+        <v>9.681443999999999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1717257615420875</v>
+        <v>0.1731587716307599</v>
       </c>
       <c r="T27">
-        <v>1.508558175295004</v>
+        <v>1.525725266905758</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.607914051696627</v>
+        <v>5.392225049708296</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1396398910067623</v>
+        <v>0.139425460856959</v>
       </c>
       <c r="C28">
-        <v>102.7711406498509</v>
+        <v>101.7931490294272</v>
       </c>
       <c r="D28">
-        <v>129.6811406498509</v>
+        <v>129.9781490294272</v>
       </c>
       <c r="E28">
-        <v>-16.95</v>
+        <v>-15.675</v>
       </c>
       <c r="F28">
-        <v>33.15</v>
+        <v>34.425</v>
       </c>
       <c r="G28">
         <v>6.24</v>
@@ -3583,28 +3583,28 @@
         <v>9.885</v>
       </c>
       <c r="M28">
-        <v>1.833195</v>
+        <v>1.9037025</v>
       </c>
       <c r="N28">
-        <v>8.051805</v>
+        <v>7.981297499999999</v>
       </c>
       <c r="O28">
-        <v>1.610361</v>
+        <v>1.5962595</v>
       </c>
       <c r="P28">
-        <v>6.441444</v>
+        <v>6.385038</v>
       </c>
       <c r="Q28">
-        <v>9.681443999999999</v>
+        <v>9.625038</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1731587716307599</v>
+        <v>0.1746310422698069</v>
       </c>
       <c r="T28">
-        <v>1.525725266905758</v>
+        <v>1.543362689793519</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.392225049708296</v>
+        <v>5.19251301083021</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.139425460856959</v>
+        <v>0.1392110307071557</v>
       </c>
       <c r="C29">
-        <v>101.7931490294272</v>
+        <v>100.8165210070892</v>
       </c>
       <c r="D29">
-        <v>129.9781490294272</v>
+        <v>130.2765210070892</v>
       </c>
       <c r="E29">
-        <v>-15.675</v>
+        <v>-14.4</v>
       </c>
       <c r="F29">
-        <v>34.425</v>
+        <v>35.7</v>
       </c>
       <c r="G29">
         <v>6.24</v>
@@ -3665,28 +3665,28 @@
         <v>9.885</v>
       </c>
       <c r="M29">
-        <v>1.9037025</v>
+        <v>1.97421</v>
       </c>
       <c r="N29">
-        <v>7.981297499999999</v>
+        <v>7.91079</v>
       </c>
       <c r="O29">
-        <v>1.5962595</v>
+        <v>1.582158</v>
       </c>
       <c r="P29">
-        <v>6.385038</v>
+        <v>6.328632</v>
       </c>
       <c r="Q29">
-        <v>9.625038</v>
+        <v>9.568632000000001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1746310422698069</v>
+        <v>0.176144209315494</v>
       </c>
       <c r="T29">
-        <v>1.543362689793519</v>
+        <v>1.561490041094828</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.19251301083021</v>
+        <v>5.007066117586274</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1392110307071557</v>
+        <v>0.1389966005573524</v>
       </c>
       <c r="C30">
-        <v>100.8165210070892</v>
+        <v>99.84126599508593</v>
       </c>
       <c r="D30">
-        <v>130.2765210070892</v>
+        <v>130.5762659950859</v>
       </c>
       <c r="E30">
-        <v>-14.4</v>
+        <v>-13.125</v>
       </c>
       <c r="F30">
-        <v>35.7</v>
+        <v>36.975</v>
       </c>
       <c r="G30">
         <v>6.24</v>
@@ -3747,28 +3747,28 @@
         <v>9.885</v>
       </c>
       <c r="M30">
-        <v>1.97421</v>
+        <v>2.0447175</v>
       </c>
       <c r="N30">
-        <v>7.91079</v>
+        <v>7.8402825</v>
       </c>
       <c r="O30">
-        <v>1.582158</v>
+        <v>1.5680565</v>
       </c>
       <c r="P30">
-        <v>6.328632</v>
+        <v>6.272226</v>
       </c>
       <c r="Q30">
-        <v>9.568632000000001</v>
+        <v>9.512226</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.176144209315494</v>
+        <v>0.1777000007850034</v>
       </c>
       <c r="T30">
-        <v>1.561490041094828</v>
+        <v>1.58012802201026</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.007066117586274</v>
+        <v>4.834408665255713</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1389966005573524</v>
+        <v>0.1387821704075491</v>
       </c>
       <c r="C31">
-        <v>99.84126599508593</v>
+        <v>98.86739349249058</v>
       </c>
       <c r="D31">
-        <v>130.5762659950859</v>
+        <v>130.8773934924906</v>
       </c>
       <c r="E31">
-        <v>-13.12500000000001</v>
+        <v>-11.85</v>
       </c>
       <c r="F31">
-        <v>36.97499999999999</v>
+        <v>38.25</v>
       </c>
       <c r="G31">
         <v>6.24</v>
@@ -3829,28 +3829,28 @@
         <v>9.885</v>
       </c>
       <c r="M31">
-        <v>2.0447175</v>
+        <v>2.115225</v>
       </c>
       <c r="N31">
-        <v>7.8402825</v>
+        <v>7.769774999999999</v>
       </c>
       <c r="O31">
-        <v>1.5680565</v>
+        <v>1.553955</v>
       </c>
       <c r="P31">
-        <v>6.272226</v>
+        <v>6.215819999999999</v>
       </c>
       <c r="Q31">
-        <v>9.512226</v>
+        <v>9.455819999999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1777000007850034</v>
+        <v>0.1793002434393559</v>
       </c>
       <c r="T31">
-        <v>1.58012802201026</v>
+        <v>1.599298516666132</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.834408665255713</v>
+        <v>4.673261709747189</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1387821704075491</v>
+        <v>0.1385677402577458</v>
       </c>
       <c r="C32">
-        <v>98.86739349249058</v>
+        <v>97.89491308620373</v>
       </c>
       <c r="D32">
-        <v>130.8773934924906</v>
+        <v>131.1799130862037</v>
       </c>
       <c r="E32">
-        <v>-11.85</v>
+        <v>-10.575</v>
       </c>
       <c r="F32">
-        <v>38.25</v>
+        <v>39.525</v>
       </c>
       <c r="G32">
         <v>6.24</v>
@@ -3911,28 +3911,28 @@
         <v>9.885</v>
       </c>
       <c r="M32">
-        <v>2.115225</v>
+        <v>2.1857325</v>
       </c>
       <c r="N32">
-        <v>7.769774999999999</v>
+        <v>7.699267499999999</v>
       </c>
       <c r="O32">
-        <v>1.553955</v>
+        <v>1.5398535</v>
       </c>
       <c r="P32">
-        <v>6.215819999999999</v>
+        <v>6.159414</v>
       </c>
       <c r="Q32">
-        <v>9.455819999999999</v>
+        <v>9.399414</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1793002434393559</v>
+        <v>0.1809468699387621</v>
       </c>
       <c r="T32">
-        <v>1.599298516666132</v>
+        <v>1.619024677833768</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.673261709747189</v>
+        <v>4.52251133201341</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1385677402577458</v>
+        <v>0.1389933101079425</v>
       </c>
       <c r="C33">
-        <v>97.89491308620373</v>
+        <v>96.02087635388622</v>
       </c>
       <c r="D33">
-        <v>131.1799130862037</v>
+        <v>130.5808763538862</v>
       </c>
       <c r="E33">
-        <v>-10.575</v>
+        <v>-9.299999999999997</v>
       </c>
       <c r="F33">
-        <v>39.525</v>
+        <v>40.8</v>
       </c>
       <c r="G33">
         <v>6.24</v>
@@ -3993,45 +3993,45 @@
         <v>9.885</v>
       </c>
       <c r="M33">
-        <v>2.1857325</v>
+        <v>2.35824</v>
       </c>
       <c r="N33">
-        <v>7.699267499999999</v>
+        <v>7.526759999999999</v>
       </c>
       <c r="O33">
-        <v>1.5398535</v>
+        <v>1.505352</v>
       </c>
       <c r="P33">
-        <v>6.159414</v>
+        <v>6.021407999999999</v>
       </c>
       <c r="Q33">
-        <v>9.399414</v>
+        <v>9.261407999999999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1809468699387621</v>
+        <v>0.1826419266293273</v>
       </c>
       <c r="T33">
-        <v>1.619024677833768</v>
+        <v>1.639331020212218</v>
       </c>
       <c r="U33">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V33">
         <v>0.2</v>
       </c>
       <c r="W33">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y33">
-        <v>4.52251133201341</v>
+        <v>4.191685324648891</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1389933101079425</v>
+        <v>0.1387988799581392</v>
       </c>
       <c r="C34">
-        <v>96.02087635388622</v>
+        <v>95.01887812941685</v>
       </c>
       <c r="D34">
-        <v>130.5808763538862</v>
+        <v>130.8538781294168</v>
       </c>
       <c r="E34">
-        <v>-9.299999999999997</v>
+        <v>-8.024999999999999</v>
       </c>
       <c r="F34">
-        <v>40.8</v>
+        <v>42.075</v>
       </c>
       <c r="G34">
         <v>6.24</v>
@@ -4075,28 +4075,28 @@
         <v>9.885</v>
       </c>
       <c r="M34">
-        <v>2.35824</v>
+        <v>2.431935</v>
       </c>
       <c r="N34">
-        <v>7.526759999999999</v>
+        <v>7.453065</v>
       </c>
       <c r="O34">
-        <v>1.505352</v>
+        <v>1.490613</v>
       </c>
       <c r="P34">
-        <v>6.021407999999999</v>
+        <v>5.962452</v>
       </c>
       <c r="Q34">
-        <v>9.261407999999999</v>
+        <v>9.202452000000001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1826419266293273</v>
+        <v>0.1843875820270735</v>
       </c>
       <c r="T34">
-        <v>1.639331020212218</v>
+        <v>1.660243522064651</v>
       </c>
       <c r="U34">
         <v>0.0578</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.191685324648891</v>
+        <v>4.064664557235288</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1387988799581392</v>
+        <v>0.1395564498083359</v>
       </c>
       <c r="C35">
-        <v>95.01887812941685</v>
+        <v>92.68655404072953</v>
       </c>
       <c r="D35">
-        <v>130.8538781294168</v>
+        <v>129.7965540407295</v>
       </c>
       <c r="E35">
-        <v>-8.024999999999999</v>
+        <v>-6.75</v>
       </c>
       <c r="F35">
-        <v>42.075</v>
+        <v>43.35</v>
       </c>
       <c r="G35">
         <v>6.24</v>
@@ -4157,45 +4157,45 @@
         <v>9.885</v>
       </c>
       <c r="M35">
-        <v>2.431935</v>
+        <v>2.657355</v>
       </c>
       <c r="N35">
-        <v>7.453065</v>
+        <v>7.227645</v>
       </c>
       <c r="O35">
-        <v>1.490613</v>
+        <v>1.445529</v>
       </c>
       <c r="P35">
-        <v>5.962452</v>
+        <v>5.782116</v>
       </c>
       <c r="Q35">
-        <v>9.202452000000001</v>
+        <v>9.022116</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1843875820270735</v>
+        <v>0.1861861360732363</v>
       </c>
       <c r="T35">
-        <v>1.660243522064651</v>
+        <v>1.68178973609443</v>
       </c>
       <c r="U35">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V35">
         <v>0.2</v>
       </c>
       <c r="W35">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y35">
-        <v>4.064664557235288</v>
+        <v>3.719864301156601</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1395564498083359</v>
+        <v>0.1393900196585326</v>
       </c>
       <c r="C36">
-        <v>92.68655404072953</v>
+        <v>91.6423698906649</v>
       </c>
       <c r="D36">
-        <v>129.7965540407295</v>
+        <v>130.0273698906649</v>
       </c>
       <c r="E36">
-        <v>-6.75</v>
+        <v>-5.474999999999994</v>
       </c>
       <c r="F36">
-        <v>43.35</v>
+        <v>44.62500000000001</v>
       </c>
       <c r="G36">
         <v>6.24</v>
@@ -4239,28 +4239,28 @@
         <v>9.885</v>
       </c>
       <c r="M36">
-        <v>2.657355</v>
+        <v>2.7355125</v>
       </c>
       <c r="N36">
-        <v>7.227645</v>
+        <v>7.149487499999999</v>
       </c>
       <c r="O36">
-        <v>1.445529</v>
+        <v>1.4298975</v>
       </c>
       <c r="P36">
-        <v>5.782116</v>
+        <v>5.719589999999999</v>
       </c>
       <c r="Q36">
-        <v>9.022116</v>
+        <v>8.959589999999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1861861360732363</v>
+        <v>0.1880400302438964</v>
       </c>
       <c r="T36">
-        <v>1.68178973609443</v>
+        <v>1.703998910555895</v>
       </c>
       <c r="U36">
         <v>0.0613</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.719864301156601</v>
+        <v>3.613582463980697</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1393900196585326</v>
+        <v>0.1392235895087293</v>
       </c>
       <c r="C37">
-        <v>91.6423698906649</v>
+        <v>90.59900811783245</v>
       </c>
       <c r="D37">
-        <v>130.0273698906649</v>
+        <v>130.2590081178325</v>
       </c>
       <c r="E37">
-        <v>-5.474999999999994</v>
+        <v>-4.199999999999996</v>
       </c>
       <c r="F37">
-        <v>44.62500000000001</v>
+        <v>45.90000000000001</v>
       </c>
       <c r="G37">
         <v>6.24</v>
@@ -4321,28 +4321,28 @@
         <v>9.885</v>
       </c>
       <c r="M37">
-        <v>2.7355125</v>
+        <v>2.813670000000001</v>
       </c>
       <c r="N37">
-        <v>7.149487499999999</v>
+        <v>7.07133</v>
       </c>
       <c r="O37">
-        <v>1.4298975</v>
+        <v>1.414266</v>
       </c>
       <c r="P37">
-        <v>5.719589999999999</v>
+        <v>5.657064</v>
       </c>
       <c r="Q37">
-        <v>8.959589999999999</v>
+        <v>8.897064</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1880400302438964</v>
+        <v>0.1899518586073896</v>
       </c>
       <c r="T37">
-        <v>1.703998910555895</v>
+        <v>1.726902121719281</v>
       </c>
       <c r="U37">
         <v>0.0613</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.613582463980697</v>
+        <v>3.513205173314567</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1392235895087294</v>
+        <v>0.1398859593589261</v>
       </c>
       <c r="C38">
-        <v>90.59900811783237</v>
+        <v>88.40697819879175</v>
       </c>
       <c r="D38">
-        <v>130.2590081178324</v>
+        <v>129.3419781987917</v>
       </c>
       <c r="E38">
-        <v>-4.200000000000003</v>
+        <v>-2.925000000000004</v>
       </c>
       <c r="F38">
-        <v>45.9</v>
+        <v>47.175</v>
       </c>
       <c r="G38">
         <v>6.24</v>
@@ -4403,45 +4403,45 @@
         <v>9.885</v>
       </c>
       <c r="M38">
-        <v>2.81367</v>
+        <v>3.0239175</v>
       </c>
       <c r="N38">
-        <v>7.07133</v>
+        <v>6.8610825</v>
       </c>
       <c r="O38">
-        <v>1.414266</v>
+        <v>1.3722165</v>
       </c>
       <c r="P38">
-        <v>5.657064</v>
+        <v>5.488866</v>
       </c>
       <c r="Q38">
-        <v>8.897064</v>
+        <v>8.728866</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1899518586073896</v>
+        <v>0.1919243799348033</v>
       </c>
       <c r="T38">
-        <v>1.726902121719281</v>
+        <v>1.750532418951345</v>
       </c>
       <c r="U38">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V38">
         <v>0.2</v>
       </c>
       <c r="W38">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y38">
-        <v>3.513205173314568</v>
+        <v>3.26893838869612</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1398859593589261</v>
+        <v>0.1397419292091228</v>
       </c>
       <c r="C39">
-        <v>88.40697819879175</v>
+        <v>87.33028309472756</v>
       </c>
       <c r="D39">
-        <v>129.3419781987917</v>
+        <v>129.5402830947276</v>
       </c>
       <c r="E39">
-        <v>-2.925000000000004</v>
+        <v>-1.649999999999999</v>
       </c>
       <c r="F39">
-        <v>47.175</v>
+        <v>48.45</v>
       </c>
       <c r="G39">
         <v>6.24</v>
@@ -4485,28 +4485,28 @@
         <v>9.885</v>
       </c>
       <c r="M39">
-        <v>3.0239175</v>
+        <v>3.105645</v>
       </c>
       <c r="N39">
-        <v>6.8610825</v>
+        <v>6.779354999999999</v>
       </c>
       <c r="O39">
-        <v>1.3722165</v>
+        <v>1.355871</v>
       </c>
       <c r="P39">
-        <v>5.488866</v>
+        <v>5.423483999999999</v>
       </c>
       <c r="Q39">
-        <v>8.728866</v>
+        <v>8.663484</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1919243799348033</v>
+        <v>0.1939605309824561</v>
       </c>
       <c r="T39">
-        <v>1.750532418951345</v>
+        <v>1.774924983836057</v>
       </c>
       <c r="U39">
         <v>0.0641</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.26893838869612</v>
+        <v>3.182913694256748</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1397419292091228</v>
+        <v>0.1395978990593195</v>
       </c>
       <c r="C40">
-        <v>87.33028309472756</v>
+        <v>86.25419699969569</v>
       </c>
       <c r="D40">
-        <v>129.5402830947276</v>
+        <v>129.7391969996957</v>
       </c>
       <c r="E40">
-        <v>-1.649999999999999</v>
+        <v>-0.375</v>
       </c>
       <c r="F40">
-        <v>48.45</v>
+        <v>49.725</v>
       </c>
       <c r="G40">
         <v>6.24</v>
@@ -4567,28 +4567,28 @@
         <v>9.885</v>
       </c>
       <c r="M40">
-        <v>3.105645</v>
+        <v>3.1873725</v>
       </c>
       <c r="N40">
-        <v>6.779354999999999</v>
+        <v>6.697627499999999</v>
       </c>
       <c r="O40">
-        <v>1.355871</v>
+        <v>1.3395255</v>
       </c>
       <c r="P40">
-        <v>5.423483999999999</v>
+        <v>5.358102</v>
       </c>
       <c r="Q40">
-        <v>8.663484</v>
+        <v>8.598102000000001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1939605309824561</v>
+        <v>0.1960634410808516</v>
       </c>
       <c r="T40">
-        <v>1.774924983836057</v>
+        <v>1.800117304946497</v>
       </c>
       <c r="U40">
         <v>0.0641</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.182913694256748</v>
+        <v>3.101300522609139</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1395978990593195</v>
+        <v>0.1394538689095162</v>
       </c>
       <c r="C41">
-        <v>86.25419699969569</v>
+        <v>85.17872272347844</v>
       </c>
       <c r="D41">
-        <v>129.7391969996957</v>
+        <v>129.9387227234784</v>
       </c>
       <c r="E41">
-        <v>-0.375</v>
+        <v>0.8999999999999986</v>
       </c>
       <c r="F41">
-        <v>49.725</v>
+        <v>51</v>
       </c>
       <c r="G41">
         <v>6.24</v>
@@ -4649,28 +4649,28 @@
         <v>9.885</v>
       </c>
       <c r="M41">
-        <v>3.1873725</v>
+        <v>3.2691</v>
       </c>
       <c r="N41">
-        <v>6.697627499999999</v>
+        <v>6.6159</v>
       </c>
       <c r="O41">
-        <v>1.3395255</v>
+        <v>1.32318</v>
       </c>
       <c r="P41">
-        <v>5.358102</v>
+        <v>5.29272</v>
       </c>
       <c r="Q41">
-        <v>8.598102000000001</v>
+        <v>8.532720000000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1960634410808516</v>
+        <v>0.1982364481825269</v>
       </c>
       <c r="T41">
-        <v>1.800117304946497</v>
+        <v>1.826149370093952</v>
       </c>
       <c r="U41">
         <v>0.0641</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.101300522609139</v>
+        <v>3.023768009543911</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1394538689095162</v>
+        <v>0.1418682387597129</v>
       </c>
       <c r="C42">
-        <v>85.17872272347844</v>
+        <v>80.63812590847573</v>
       </c>
       <c r="D42">
-        <v>129.9387227234784</v>
+        <v>126.6731259084757</v>
       </c>
       <c r="E42">
-        <v>0.8999999999999986</v>
+        <v>2.175000000000004</v>
       </c>
       <c r="F42">
-        <v>51</v>
+        <v>52.27500000000001</v>
       </c>
       <c r="G42">
         <v>6.24</v>
@@ -4731,45 +4731,45 @@
         <v>9.885</v>
       </c>
       <c r="M42">
-        <v>3.2691</v>
+        <v>3.758572500000001</v>
       </c>
       <c r="N42">
-        <v>6.6159</v>
+        <v>6.126427499999999</v>
       </c>
       <c r="O42">
-        <v>1.32318</v>
+        <v>1.2252855</v>
       </c>
       <c r="P42">
-        <v>5.29272</v>
+        <v>4.901141999999999</v>
       </c>
       <c r="Q42">
-        <v>8.532720000000001</v>
+        <v>8.141141999999999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1982364481825269</v>
+        <v>0.2004831165418862</v>
       </c>
       <c r="T42">
-        <v>1.826149370093952</v>
+        <v>1.853063878127761</v>
       </c>
       <c r="U42">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V42">
         <v>0.2</v>
       </c>
       <c r="W42">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y42">
-        <v>3.023768009543911</v>
+        <v>2.629987847779975</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1418682387597129</v>
+        <v>0.1417866086099096</v>
       </c>
       <c r="C43">
-        <v>80.63812590847573</v>
+        <v>79.47085287574453</v>
       </c>
       <c r="D43">
-        <v>126.6731259084757</v>
+        <v>126.7808528757445</v>
       </c>
       <c r="E43">
-        <v>2.175000000000004</v>
+        <v>3.450000000000003</v>
       </c>
       <c r="F43">
-        <v>52.27500000000001</v>
+        <v>53.55</v>
       </c>
       <c r="G43">
         <v>6.24</v>
@@ -4813,28 +4813,28 @@
         <v>9.885</v>
       </c>
       <c r="M43">
-        <v>3.758572500000001</v>
+        <v>3.850245000000001</v>
       </c>
       <c r="N43">
-        <v>6.126427499999999</v>
+        <v>6.034754999999999</v>
       </c>
       <c r="O43">
-        <v>1.2252855</v>
+        <v>1.206951</v>
       </c>
       <c r="P43">
-        <v>4.901141999999999</v>
+        <v>4.827803999999999</v>
       </c>
       <c r="Q43">
-        <v>8.141141999999999</v>
+        <v>8.067803999999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2004831165418862</v>
+        <v>0.202807256223982</v>
       </c>
       <c r="T43">
-        <v>1.853063878127761</v>
+        <v>1.880906472645495</v>
       </c>
       <c r="U43">
         <v>0.07190000000000001</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.629987847779975</v>
+        <v>2.567369089499499</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1417866086099096</v>
+        <v>0.1417049784601063</v>
       </c>
       <c r="C44">
-        <v>79.47085287574454</v>
+        <v>78.30376322803914</v>
       </c>
       <c r="D44">
-        <v>126.7808528757445</v>
+        <v>126.8887632280391</v>
       </c>
       <c r="E44">
-        <v>3.449999999999996</v>
+        <v>4.724999999999994</v>
       </c>
       <c r="F44">
-        <v>53.55</v>
+        <v>54.825</v>
       </c>
       <c r="G44">
         <v>6.24</v>
@@ -4895,28 +4895,28 @@
         <v>9.885</v>
       </c>
       <c r="M44">
-        <v>3.850245</v>
+        <v>3.9419175</v>
       </c>
       <c r="N44">
-        <v>6.034755</v>
+        <v>5.943082499999999</v>
       </c>
       <c r="O44">
-        <v>1.206951</v>
+        <v>1.1886165</v>
       </c>
       <c r="P44">
-        <v>4.827804</v>
+        <v>4.754465999999999</v>
       </c>
       <c r="Q44">
-        <v>8.067803999999999</v>
+        <v>7.994465999999999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.202807256223982</v>
+        <v>0.2052129446668531</v>
       </c>
       <c r="T44">
-        <v>1.880906472645494</v>
+        <v>1.909726000304202</v>
       </c>
       <c r="U44">
         <v>0.07190000000000001</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.567369089499499</v>
+        <v>2.507662831604162</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1417049784601063</v>
+        <v>0.142996148310303</v>
       </c>
       <c r="C45">
-        <v>78.30376322803914</v>
+        <v>75.34315172740907</v>
       </c>
       <c r="D45">
-        <v>126.8887632280391</v>
+        <v>125.2031517274091</v>
       </c>
       <c r="E45">
-        <v>4.724999999999994</v>
+        <v>6</v>
       </c>
       <c r="F45">
-        <v>54.825</v>
+        <v>56.1</v>
       </c>
       <c r="G45">
         <v>6.24</v>
@@ -4977,45 +4977,45 @@
         <v>9.885</v>
       </c>
       <c r="M45">
-        <v>3.9419175</v>
+        <v>4.25238</v>
       </c>
       <c r="N45">
-        <v>5.943082499999999</v>
+        <v>5.632619999999999</v>
       </c>
       <c r="O45">
-        <v>1.1886165</v>
+        <v>1.126524</v>
       </c>
       <c r="P45">
-        <v>4.754465999999999</v>
+        <v>4.506095999999999</v>
       </c>
       <c r="Q45">
-        <v>7.994465999999999</v>
+        <v>7.746096</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2052129446668531</v>
+        <v>0.2077045505541125</v>
       </c>
       <c r="T45">
-        <v>1.909726000304202</v>
+        <v>1.939574796807862</v>
       </c>
       <c r="U45">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V45">
         <v>0.2</v>
       </c>
       <c r="W45">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y45">
-        <v>2.507662831604162</v>
+        <v>2.324580587812001</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.142996148310303</v>
+        <v>0.1429457181604997</v>
       </c>
       <c r="C46">
-        <v>75.34315172740907</v>
+        <v>74.13314701301732</v>
       </c>
       <c r="D46">
-        <v>125.2031517274091</v>
+        <v>125.2681470130173</v>
       </c>
       <c r="E46">
-        <v>6</v>
+        <v>7.274999999999999</v>
       </c>
       <c r="F46">
-        <v>56.1</v>
+        <v>57.375</v>
       </c>
       <c r="G46">
         <v>6.24</v>
@@ -5059,28 +5059,28 @@
         <v>9.885</v>
       </c>
       <c r="M46">
-        <v>4.25238</v>
+        <v>4.349025</v>
       </c>
       <c r="N46">
-        <v>5.632619999999999</v>
+        <v>5.535975</v>
       </c>
       <c r="O46">
-        <v>1.126524</v>
+        <v>1.107195</v>
       </c>
       <c r="P46">
-        <v>4.506095999999999</v>
+        <v>4.42878</v>
       </c>
       <c r="Q46">
-        <v>7.746096</v>
+        <v>7.66878</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2077045505541125</v>
+        <v>0.2102867602918176</v>
       </c>
       <c r="T46">
-        <v>1.939574796807862</v>
+        <v>1.970509004093474</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.324580587812001</v>
+        <v>2.272923241416179</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1429457181604997</v>
+        <v>0.1428952880106964</v>
       </c>
       <c r="C47">
-        <v>74.13314701301732</v>
+        <v>72.92320981419826</v>
       </c>
       <c r="D47">
-        <v>125.2681470130173</v>
+        <v>125.3332098141983</v>
       </c>
       <c r="E47">
-        <v>7.274999999999999</v>
+        <v>8.550000000000004</v>
       </c>
       <c r="F47">
-        <v>57.375</v>
+        <v>58.65000000000001</v>
       </c>
       <c r="G47">
         <v>6.24</v>
@@ -5141,28 +5141,28 @@
         <v>9.885</v>
       </c>
       <c r="M47">
-        <v>4.349025</v>
+        <v>4.445670000000001</v>
       </c>
       <c r="N47">
-        <v>5.535975</v>
+        <v>5.439329999999999</v>
       </c>
       <c r="O47">
-        <v>1.107195</v>
+        <v>1.087866</v>
       </c>
       <c r="P47">
-        <v>4.42878</v>
+        <v>4.351463999999999</v>
       </c>
       <c r="Q47">
-        <v>7.66878</v>
+        <v>7.591463999999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2102867602918176</v>
+        <v>0.2129646074272155</v>
       </c>
       <c r="T47">
-        <v>1.970509004093474</v>
+        <v>2.002588922760034</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.272923241416179</v>
+        <v>2.223511866602784</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1428952880106964</v>
+        <v>0.1428448578608931</v>
       </c>
       <c r="C48">
-        <v>72.92320981419826</v>
+        <v>71.71334023620699</v>
       </c>
       <c r="D48">
-        <v>125.3332098141983</v>
+        <v>125.398340236207</v>
       </c>
       <c r="E48">
-        <v>8.550000000000004</v>
+        <v>9.825000000000003</v>
       </c>
       <c r="F48">
-        <v>58.65000000000001</v>
+        <v>59.925</v>
       </c>
       <c r="G48">
         <v>6.24</v>
@@ -5223,28 +5223,28 @@
         <v>9.885</v>
       </c>
       <c r="M48">
-        <v>4.445670000000001</v>
+        <v>4.542315</v>
       </c>
       <c r="N48">
-        <v>5.439329999999999</v>
+        <v>5.342684999999999</v>
       </c>
       <c r="O48">
-        <v>1.087866</v>
+        <v>1.068537</v>
       </c>
       <c r="P48">
-        <v>4.351463999999999</v>
+        <v>4.274147999999999</v>
       </c>
       <c r="Q48">
-        <v>7.591463999999999</v>
+        <v>7.514148</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2129646074272155</v>
+        <v>0.2157435053979115</v>
       </c>
       <c r="T48">
-        <v>2.002588922760034</v>
+        <v>2.035879404395144</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.223511866602784</v>
+        <v>2.176203103483576</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1428448578608931</v>
+        <v>0.1427944277110898</v>
       </c>
       <c r="C49">
-        <v>71.71334023620699</v>
+        <v>70.50353838451743</v>
       </c>
       <c r="D49">
-        <v>125.398340236207</v>
+        <v>125.4635383845174</v>
       </c>
       <c r="E49">
-        <v>9.825000000000003</v>
+        <v>11.1</v>
       </c>
       <c r="F49">
-        <v>59.925</v>
+        <v>61.2</v>
       </c>
       <c r="G49">
         <v>6.24</v>
@@ -5305,28 +5305,28 @@
         <v>9.885</v>
       </c>
       <c r="M49">
-        <v>4.542315</v>
+        <v>4.638960000000001</v>
       </c>
       <c r="N49">
-        <v>5.342684999999999</v>
+        <v>5.246039999999999</v>
       </c>
       <c r="O49">
-        <v>1.068537</v>
+        <v>1.049208</v>
       </c>
       <c r="P49">
-        <v>4.274147999999999</v>
+        <v>4.196831999999999</v>
       </c>
       <c r="Q49">
-        <v>7.514148</v>
+        <v>7.436831999999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2157435053979115</v>
+        <v>0.2186292840597881</v>
       </c>
       <c r="T49">
-        <v>2.035879404395144</v>
+        <v>2.070450289170066</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.176203103483576</v>
+        <v>2.130865538827668</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1427944277110898</v>
+        <v>0.1427439975612865</v>
       </c>
       <c r="C50">
-        <v>70.50353838451744</v>
+        <v>69.2938043648231</v>
       </c>
       <c r="D50">
-        <v>125.4635383845174</v>
+        <v>125.5288043648231</v>
       </c>
       <c r="E50">
-        <v>11.09999999999999</v>
+        <v>12.375</v>
       </c>
       <c r="F50">
-        <v>61.2</v>
+        <v>62.475</v>
       </c>
       <c r="G50">
         <v>6.24</v>
@@ -5387,28 +5387,28 @@
         <v>9.885</v>
       </c>
       <c r="M50">
-        <v>4.63896</v>
+        <v>4.735605000000001</v>
       </c>
       <c r="N50">
-        <v>5.24604</v>
+        <v>5.149394999999999</v>
       </c>
       <c r="O50">
-        <v>1.049208</v>
+        <v>1.029879</v>
       </c>
       <c r="P50">
-        <v>4.196832</v>
+        <v>4.119515999999999</v>
       </c>
       <c r="Q50">
-        <v>7.436832</v>
+        <v>7.359515999999999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2186292840597881</v>
+        <v>0.2216282305123265</v>
       </c>
       <c r="T50">
-        <v>2.070450289170066</v>
+        <v>2.106376894916553</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.130865538827668</v>
+        <v>2.087378487014858</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1427439975612865</v>
+        <v>0.1426935674114832</v>
       </c>
       <c r="C51">
-        <v>69.2938043648231</v>
+        <v>68.08413828303733</v>
       </c>
       <c r="D51">
-        <v>125.5288043648231</v>
+        <v>125.5941382830373</v>
       </c>
       <c r="E51">
-        <v>12.375</v>
+        <v>13.65</v>
       </c>
       <c r="F51">
-        <v>62.475</v>
+        <v>63.75</v>
       </c>
       <c r="G51">
         <v>6.24</v>
@@ -5469,28 +5469,28 @@
         <v>9.885</v>
       </c>
       <c r="M51">
-        <v>4.735605000000001</v>
+        <v>4.83225</v>
       </c>
       <c r="N51">
-        <v>5.149394999999999</v>
+        <v>5.05275</v>
       </c>
       <c r="O51">
-        <v>1.029879</v>
+        <v>1.01055</v>
       </c>
       <c r="P51">
-        <v>4.119515999999999</v>
+        <v>4.042199999999999</v>
       </c>
       <c r="Q51">
-        <v>7.359515999999999</v>
+        <v>7.2822</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2216282305123265</v>
+        <v>0.2247471348229664</v>
       </c>
       <c r="T51">
-        <v>2.106376894916553</v>
+        <v>2.1437405648929</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.087378487014858</v>
+        <v>2.045630917274561</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1426935674114832</v>
+        <v>0.1426431372616799</v>
       </c>
       <c r="C52">
-        <v>68.08413828303733</v>
+        <v>66.87454024529424</v>
       </c>
       <c r="D52">
-        <v>125.5941382830373</v>
+        <v>125.6595402452942</v>
       </c>
       <c r="E52">
-        <v>13.65</v>
+        <v>14.925</v>
       </c>
       <c r="F52">
-        <v>63.75</v>
+        <v>65.02500000000001</v>
       </c>
       <c r="G52">
         <v>6.24</v>
@@ -5551,28 +5551,28 @@
         <v>9.885</v>
       </c>
       <c r="M52">
-        <v>4.83225</v>
+        <v>4.928895000000001</v>
       </c>
       <c r="N52">
-        <v>5.05275</v>
+        <v>4.956104999999999</v>
       </c>
       <c r="O52">
-        <v>1.01055</v>
+        <v>0.9912209999999999</v>
       </c>
       <c r="P52">
-        <v>4.042199999999999</v>
+        <v>3.964883999999999</v>
       </c>
       <c r="Q52">
-        <v>7.2822</v>
+        <v>7.204884</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2247471348229664</v>
+        <v>0.2279933413503672</v>
       </c>
       <c r="T52">
-        <v>2.1437405648929</v>
+        <v>2.182629282623384</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.045630917274561</v>
+        <v>2.005520507131923</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1426431372616799</v>
+        <v>0.1484999071118766</v>
       </c>
       <c r="C53">
-        <v>66.87454024529424</v>
+        <v>58.43342853794383</v>
       </c>
       <c r="D53">
-        <v>125.6595402452942</v>
+        <v>118.4934285379438</v>
       </c>
       <c r="E53">
-        <v>14.925</v>
+        <v>16.2</v>
       </c>
       <c r="F53">
-        <v>65.02500000000001</v>
+        <v>66.3</v>
       </c>
       <c r="G53">
         <v>6.24</v>
@@ -5633,45 +5633,45 @@
         <v>9.885</v>
       </c>
       <c r="M53">
-        <v>4.928895000000001</v>
+        <v>5.967</v>
       </c>
       <c r="N53">
-        <v>4.956104999999999</v>
+        <v>3.918</v>
       </c>
       <c r="O53">
-        <v>0.9912209999999999</v>
+        <v>0.7836000000000001</v>
       </c>
       <c r="P53">
-        <v>3.964883999999999</v>
+        <v>3.1344</v>
       </c>
       <c r="Q53">
-        <v>7.204884</v>
+        <v>6.374400000000001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2279933413503672</v>
+        <v>0.2313748064830763</v>
       </c>
       <c r="T53">
-        <v>2.182629282623384</v>
+        <v>2.223138363592637</v>
       </c>
       <c r="U53">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V53">
         <v>0.2</v>
       </c>
       <c r="W53">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y53">
-        <v>2.005520507131923</v>
+        <v>1.656611362493716</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1484999071118766</v>
+        <v>0.1485630769620733</v>
       </c>
       <c r="C54">
-        <v>58.43342853794383</v>
+        <v>57.08558902835226</v>
       </c>
       <c r="D54">
-        <v>118.4934285379438</v>
+        <v>118.4205890283523</v>
       </c>
       <c r="E54">
-        <v>16.2</v>
+        <v>17.475</v>
       </c>
       <c r="F54">
-        <v>66.3</v>
+        <v>67.575</v>
       </c>
       <c r="G54">
         <v>6.24</v>
@@ -5715,28 +5715,28 @@
         <v>9.885</v>
       </c>
       <c r="M54">
-        <v>5.967</v>
+        <v>6.08175</v>
       </c>
       <c r="N54">
-        <v>3.918</v>
+        <v>3.803249999999999</v>
       </c>
       <c r="O54">
-        <v>0.7836000000000001</v>
+        <v>0.7606499999999999</v>
       </c>
       <c r="P54">
-        <v>3.1344</v>
+        <v>3.042599999999999</v>
       </c>
       <c r="Q54">
-        <v>6.374400000000001</v>
+        <v>6.2826</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2313748064830763</v>
+        <v>0.2349001637490922</v>
       </c>
       <c r="T54">
-        <v>2.223138363592637</v>
+        <v>2.265371235241434</v>
       </c>
       <c r="U54">
         <v>0.09</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.656611362493716</v>
+        <v>1.625354544333456</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1485630769620733</v>
+        <v>0.14862624681227</v>
       </c>
       <c r="C55">
-        <v>57.08558902835226</v>
+        <v>55.73783901460544</v>
       </c>
       <c r="D55">
-        <v>118.4205890283523</v>
+        <v>118.3478390146055</v>
       </c>
       <c r="E55">
-        <v>17.475</v>
+        <v>18.75000000000001</v>
       </c>
       <c r="F55">
-        <v>67.575</v>
+        <v>68.85000000000001</v>
       </c>
       <c r="G55">
         <v>6.24</v>
@@ -5797,28 +5797,28 @@
         <v>9.885</v>
       </c>
       <c r="M55">
-        <v>6.08175</v>
+        <v>6.1965</v>
       </c>
       <c r="N55">
-        <v>3.803249999999999</v>
+        <v>3.688499999999999</v>
       </c>
       <c r="O55">
-        <v>0.7606499999999999</v>
+        <v>0.7376999999999999</v>
       </c>
       <c r="P55">
-        <v>3.042599999999999</v>
+        <v>2.9508</v>
       </c>
       <c r="Q55">
-        <v>6.2826</v>
+        <v>6.190799999999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2349001637490922</v>
+        <v>0.2385787974179783</v>
       </c>
       <c r="T55">
-        <v>2.265371235241434</v>
+        <v>2.309440318701047</v>
       </c>
       <c r="U55">
         <v>0.09</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.625354544333456</v>
+        <v>1.595255386105059</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.14862624681227</v>
+        <v>0.1486894166624667</v>
       </c>
       <c r="C56">
-        <v>55.73783901460544</v>
+        <v>54.3901783318631</v>
       </c>
       <c r="D56">
-        <v>118.3478390146055</v>
+        <v>118.2751783318631</v>
       </c>
       <c r="E56">
-        <v>18.75000000000001</v>
+        <v>20.025</v>
       </c>
       <c r="F56">
-        <v>68.85000000000001</v>
+        <v>70.125</v>
       </c>
       <c r="G56">
         <v>6.24</v>
@@ -5879,28 +5879,28 @@
         <v>9.885</v>
       </c>
       <c r="M56">
-        <v>6.1965</v>
+        <v>6.311249999999999</v>
       </c>
       <c r="N56">
-        <v>3.688499999999999</v>
+        <v>3.57375</v>
       </c>
       <c r="O56">
-        <v>0.7376999999999999</v>
+        <v>0.7147500000000001</v>
       </c>
       <c r="P56">
-        <v>2.9508</v>
+        <v>2.859</v>
       </c>
       <c r="Q56">
-        <v>6.190799999999999</v>
+        <v>6.099</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2385787974179783</v>
+        <v>0.2424209259165928</v>
       </c>
       <c r="T56">
-        <v>2.309440318701047</v>
+        <v>2.355468028092199</v>
       </c>
       <c r="U56">
         <v>0.09</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.595255386105059</v>
+        <v>1.566250742721331</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1486894166624667</v>
+        <v>0.1487525865126634</v>
       </c>
       <c r="C57">
-        <v>54.3901783318631</v>
+        <v>53.04260681568955</v>
       </c>
       <c r="D57">
-        <v>118.2751783318631</v>
+        <v>118.2026068156896</v>
       </c>
       <c r="E57">
-        <v>20.025</v>
+        <v>21.3</v>
       </c>
       <c r="F57">
-        <v>70.125</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G57">
         <v>6.24</v>
@@ -5961,28 +5961,28 @@
         <v>9.885</v>
       </c>
       <c r="M57">
-        <v>6.311249999999999</v>
+        <v>6.426</v>
       </c>
       <c r="N57">
-        <v>3.57375</v>
+        <v>3.459</v>
       </c>
       <c r="O57">
-        <v>0.7147500000000001</v>
+        <v>0.6918</v>
       </c>
       <c r="P57">
-        <v>2.859</v>
+        <v>2.7672</v>
       </c>
       <c r="Q57">
-        <v>6.099</v>
+        <v>6.0072</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2424209259165928</v>
+        <v>0.2464376966196896</v>
       </c>
       <c r="T57">
-        <v>2.355468028092199</v>
+        <v>2.40358790609204</v>
       </c>
       <c r="U57">
         <v>0.09</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.566250742721331</v>
+        <v>1.53828197945845</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1487525865126634</v>
+        <v>0.1488157563628601</v>
       </c>
       <c r="C58">
-        <v>53.04260681568955</v>
+        <v>51.69512430205246</v>
       </c>
       <c r="D58">
-        <v>118.2026068156896</v>
+        <v>118.1301243020525</v>
       </c>
       <c r="E58">
-        <v>21.3</v>
+        <v>22.57500000000001</v>
       </c>
       <c r="F58">
-        <v>71.40000000000001</v>
+        <v>72.67500000000001</v>
       </c>
       <c r="G58">
         <v>6.24</v>
@@ -6043,28 +6043,28 @@
         <v>9.885</v>
       </c>
       <c r="M58">
-        <v>6.426</v>
+        <v>6.540750000000001</v>
       </c>
       <c r="N58">
-        <v>3.459</v>
+        <v>3.344249999999999</v>
       </c>
       <c r="O58">
-        <v>0.6918</v>
+        <v>0.6688499999999998</v>
       </c>
       <c r="P58">
-        <v>2.7672</v>
+        <v>2.675399999999999</v>
       </c>
       <c r="Q58">
-        <v>6.0072</v>
+        <v>5.915399999999999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2464376966196896</v>
+        <v>0.2506412938671166</v>
       </c>
       <c r="T58">
-        <v>2.40358790609204</v>
+        <v>2.453945917952338</v>
       </c>
       <c r="U58">
         <v>0.09</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.53828197945845</v>
+        <v>1.511294576310056</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1488157563628601</v>
+        <v>0.1777883856309017</v>
       </c>
       <c r="C59">
-        <v>51.69512430205246</v>
+        <v>24.48950714637346</v>
       </c>
       <c r="D59">
-        <v>118.1301243020525</v>
+        <v>92.19950714637346</v>
       </c>
       <c r="E59">
-        <v>22.57500000000001</v>
+        <v>23.85</v>
       </c>
       <c r="F59">
-        <v>72.67500000000001</v>
+        <v>73.95</v>
       </c>
       <c r="G59">
         <v>6.24</v>
@@ -6125,45 +6125,45 @@
         <v>9.885</v>
       </c>
       <c r="M59">
-        <v>6.540750000000001</v>
+        <v>10.85586</v>
       </c>
       <c r="N59">
-        <v>3.344249999999999</v>
+        <v>-0.9708600000000018</v>
       </c>
       <c r="O59">
-        <v>0.6688499999999998</v>
+        <v>-0.1941720000000004</v>
       </c>
       <c r="P59">
-        <v>2.675399999999999</v>
+        <v>-0.7766880000000015</v>
       </c>
       <c r="Q59">
-        <v>5.915399999999999</v>
+        <v>2.463311999999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2506412938671166</v>
+        <v>0.2575006380567688</v>
       </c>
       <c r="T59">
-        <v>2.453945917952338</v>
+        <v>2.536119093859666</v>
       </c>
       <c r="U59">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.2</v>
+        <v>0.1821136234255047</v>
       </c>
       <c r="W59">
-        <v>0.07199999999999999</v>
+        <v>0.1200657200811359</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y59">
-        <v>1.511294576310056</v>
+        <v>0.9105681171275236</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1777883856309017</v>
+        <v>0.1787983856309017</v>
       </c>
       <c r="C60">
-        <v>24.48950714637347</v>
+        <v>22.51433697681766</v>
       </c>
       <c r="D60">
-        <v>92.19950714637346</v>
+        <v>91.49933697681766</v>
       </c>
       <c r="E60">
-        <v>23.84999999999999</v>
+        <v>25.12499999999999</v>
       </c>
       <c r="F60">
-        <v>73.94999999999999</v>
+        <v>75.22499999999999</v>
       </c>
       <c r="G60">
         <v>6.24</v>
@@ -6207,37 +6207,37 @@
         <v>9.885</v>
       </c>
       <c r="M60">
-        <v>10.85586</v>
+        <v>11.04303</v>
       </c>
       <c r="N60">
-        <v>-0.9708600000000001</v>
+        <v>-1.15803</v>
       </c>
       <c r="O60">
-        <v>-0.194172</v>
+        <v>-0.231606</v>
       </c>
       <c r="P60">
-        <v>-0.776688</v>
+        <v>-0.9264240000000001</v>
       </c>
       <c r="Q60">
-        <v>2.463312</v>
+        <v>2.313576</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2575006380567688</v>
+        <v>0.2626640682532754</v>
       </c>
       <c r="T60">
-        <v>2.536119093859666</v>
+        <v>2.597975657124536</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.1821136234255047</v>
+        <v>0.1790269518420216</v>
       </c>
       <c r="W60">
-        <v>0.1200657200811359</v>
+        <v>0.1205188434695912</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.9105681171275237</v>
+        <v>0.8951347592101081</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1787983856309017</v>
+        <v>0.1798083856309017</v>
       </c>
       <c r="C61">
-        <v>22.51433697681766</v>
+        <v>20.54972095083909</v>
       </c>
       <c r="D61">
-        <v>91.49933697681766</v>
+        <v>90.80972095083909</v>
       </c>
       <c r="E61">
-        <v>25.12499999999999</v>
+        <v>26.4</v>
       </c>
       <c r="F61">
-        <v>75.22499999999999</v>
+        <v>76.5</v>
       </c>
       <c r="G61">
         <v>6.24</v>
@@ -6289,37 +6289,37 @@
         <v>9.885</v>
       </c>
       <c r="M61">
-        <v>11.04303</v>
+        <v>11.2302</v>
       </c>
       <c r="N61">
-        <v>-1.15803</v>
+        <v>-1.345200000000002</v>
       </c>
       <c r="O61">
-        <v>-0.231606</v>
+        <v>-0.2690400000000004</v>
       </c>
       <c r="P61">
-        <v>-0.9264240000000001</v>
+        <v>-1.076160000000002</v>
       </c>
       <c r="Q61">
-        <v>2.313576</v>
+        <v>2.163839999999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2626640682532754</v>
+        <v>0.2680856699596072</v>
       </c>
       <c r="T61">
-        <v>2.597975657124536</v>
+        <v>2.662925048552649</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.1790269518420216</v>
+        <v>0.1760431693113212</v>
       </c>
       <c r="W61">
-        <v>0.1205188434695912</v>
+        <v>0.1209568627450981</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8951347592101081</v>
+        <v>0.8802158465566061</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1798083856309017</v>
+        <v>0.1808183856309017</v>
       </c>
       <c r="C62">
-        <v>20.54972095083909</v>
+        <v>18.59542221880511</v>
       </c>
       <c r="D62">
-        <v>90.80972095083909</v>
+        <v>90.13042221880511</v>
       </c>
       <c r="E62">
-        <v>26.4</v>
+        <v>27.67499999999999</v>
       </c>
       <c r="F62">
-        <v>76.5</v>
+        <v>77.77499999999999</v>
       </c>
       <c r="G62">
         <v>6.24</v>
@@ -6371,37 +6371,37 @@
         <v>9.885</v>
       </c>
       <c r="M62">
-        <v>11.2302</v>
+        <v>11.41737</v>
       </c>
       <c r="N62">
-        <v>-1.345200000000002</v>
+        <v>-1.53237</v>
       </c>
       <c r="O62">
-        <v>-0.2690400000000004</v>
+        <v>-0.3064740000000001</v>
       </c>
       <c r="P62">
-        <v>-1.076160000000002</v>
+        <v>-1.225896</v>
       </c>
       <c r="Q62">
-        <v>2.163839999999999</v>
+        <v>2.014104</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2680856699596072</v>
+        <v>0.2737853025226741</v>
       </c>
       <c r="T62">
-        <v>2.662925048552649</v>
+        <v>2.731205178002717</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.1760431693113212</v>
+        <v>0.1731572157160537</v>
       </c>
       <c r="W62">
-        <v>0.1209568627450981</v>
+        <v>0.1213805207328833</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8802158465566061</v>
+        <v>0.8657860785802685</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1808183856309017</v>
+        <v>0.1818283856309017</v>
       </c>
       <c r="C63">
-        <v>18.59542221880511</v>
+        <v>16.65121096544217</v>
       </c>
       <c r="D63">
-        <v>90.13042221880511</v>
+        <v>89.46121096544218</v>
       </c>
       <c r="E63">
-        <v>27.67499999999999</v>
+        <v>28.95</v>
       </c>
       <c r="F63">
-        <v>77.77499999999999</v>
+        <v>79.05</v>
       </c>
       <c r="G63">
         <v>6.24</v>
@@ -6453,37 +6453,37 @@
         <v>9.885</v>
       </c>
       <c r="M63">
-        <v>11.41737</v>
+        <v>11.60454</v>
       </c>
       <c r="N63">
-        <v>-1.53237</v>
+        <v>-1.71954</v>
       </c>
       <c r="O63">
-        <v>-0.3064740000000001</v>
+        <v>-0.3439080000000001</v>
       </c>
       <c r="P63">
-        <v>-1.225896</v>
+        <v>-1.375632</v>
       </c>
       <c r="Q63">
-        <v>2.014104</v>
+        <v>1.864368</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2737853025226741</v>
+        <v>0.279784915746955</v>
       </c>
       <c r="T63">
-        <v>2.731205178002717</v>
+        <v>2.803078998476472</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.1731572157160537</v>
+        <v>0.1703643573980528</v>
       </c>
       <c r="W63">
-        <v>0.1213805207328833</v>
+        <v>0.1217905123339658</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8657860785802685</v>
+        <v>0.8518217869902641</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1818283856309017</v>
+        <v>0.1828383856309017</v>
       </c>
       <c r="C64">
-        <v>16.65121096544217</v>
+        <v>14.71686415061275</v>
       </c>
       <c r="D64">
-        <v>89.46121096544218</v>
+        <v>88.80186415061276</v>
       </c>
       <c r="E64">
-        <v>28.95</v>
+        <v>30.225</v>
       </c>
       <c r="F64">
-        <v>79.05</v>
+        <v>80.325</v>
       </c>
       <c r="G64">
         <v>6.24</v>
@@ -6535,37 +6535,37 @@
         <v>9.885</v>
       </c>
       <c r="M64">
-        <v>11.60454</v>
+        <v>11.79171</v>
       </c>
       <c r="N64">
-        <v>-1.71954</v>
+        <v>-1.906710000000002</v>
       </c>
       <c r="O64">
-        <v>-0.3439080000000001</v>
+        <v>-0.3813420000000005</v>
       </c>
       <c r="P64">
-        <v>-1.375632</v>
+        <v>-1.525368000000002</v>
       </c>
       <c r="Q64">
-        <v>1.864368</v>
+        <v>1.714631999999999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.279784915746955</v>
+        <v>0.2861088323887646</v>
       </c>
       <c r="T64">
-        <v>2.803078998476472</v>
+        <v>2.878837890327188</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.1703643573980528</v>
+        <v>0.1676601612488774</v>
       </c>
       <c r="W64">
-        <v>0.1217905123339658</v>
+        <v>0.1221874883286648</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8518217869902641</v>
+        <v>0.8383008062443869</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1828383856309017</v>
+        <v>0.1838483856309017</v>
       </c>
       <c r="C65">
-        <v>14.71686415061275</v>
+        <v>12.79216526147165</v>
       </c>
       <c r="D65">
-        <v>88.80186415061276</v>
+        <v>88.15216526147167</v>
       </c>
       <c r="E65">
-        <v>30.225</v>
+        <v>31.50000000000001</v>
       </c>
       <c r="F65">
-        <v>80.325</v>
+        <v>81.60000000000001</v>
       </c>
       <c r="G65">
         <v>6.24</v>
@@ -6617,37 +6617,37 @@
         <v>9.885</v>
       </c>
       <c r="M65">
-        <v>11.79171</v>
+        <v>11.97888</v>
       </c>
       <c r="N65">
-        <v>-1.906710000000002</v>
+        <v>-2.093880000000002</v>
       </c>
       <c r="O65">
-        <v>-0.3813420000000005</v>
+        <v>-0.4187760000000005</v>
       </c>
       <c r="P65">
-        <v>-1.525368000000002</v>
+        <v>-1.675104000000002</v>
       </c>
       <c r="Q65">
-        <v>1.714631999999999</v>
+        <v>1.564895999999999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2861088323887646</v>
+        <v>0.2927840777328969</v>
       </c>
       <c r="T65">
-        <v>2.878837890327188</v>
+        <v>2.958805609502943</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.1676601612488774</v>
+        <v>0.1650404712293637</v>
       </c>
       <c r="W65">
-        <v>0.1221874883286648</v>
+        <v>0.1225720588235294</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8383008062443869</v>
+        <v>0.8252023561468182</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1838483856309017</v>
+        <v>0.1848583856309017</v>
       </c>
       <c r="C66">
-        <v>12.79216526147165</v>
+        <v>10.87690407542276</v>
       </c>
       <c r="D66">
-        <v>88.15216526147167</v>
+        <v>87.51190407542276</v>
       </c>
       <c r="E66">
-        <v>31.50000000000001</v>
+        <v>32.775</v>
       </c>
       <c r="F66">
-        <v>81.60000000000001</v>
+        <v>82.875</v>
       </c>
       <c r="G66">
         <v>6.24</v>
@@ -6699,37 +6699,37 @@
         <v>9.885</v>
       </c>
       <c r="M66">
-        <v>11.97888</v>
+        <v>12.16605</v>
       </c>
       <c r="N66">
-        <v>-2.093880000000002</v>
+        <v>-2.281050000000002</v>
       </c>
       <c r="O66">
-        <v>-0.4187760000000005</v>
+        <v>-0.4562100000000004</v>
       </c>
       <c r="P66">
-        <v>-1.675104000000002</v>
+        <v>-1.824840000000002</v>
       </c>
       <c r="Q66">
-        <v>1.564895999999999</v>
+        <v>1.415159999999998</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2927840777328969</v>
+        <v>0.2998407656681226</v>
       </c>
       <c r="T66">
-        <v>2.958805609502943</v>
+        <v>3.043342912631599</v>
       </c>
       <c r="U66">
         <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.1650404712293637</v>
+        <v>0.1625013870566042</v>
       </c>
       <c r="W66">
-        <v>0.1225720588235294</v>
+        <v>0.1229447963800905</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.8252023561468182</v>
+        <v>0.812506935283021</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1848583856309017</v>
+        <v>0.1858683856309017</v>
       </c>
       <c r="C67">
-        <v>10.87690407542276</v>
+        <v>8.970876433331625</v>
       </c>
       <c r="D67">
-        <v>87.51190407542276</v>
+        <v>86.88087643333164</v>
       </c>
       <c r="E67">
-        <v>32.775</v>
+        <v>34.05</v>
       </c>
       <c r="F67">
-        <v>82.875</v>
+        <v>84.15000000000001</v>
       </c>
       <c r="G67">
         <v>6.24</v>
@@ -6781,37 +6781,37 @@
         <v>9.885</v>
       </c>
       <c r="M67">
-        <v>12.16605</v>
+        <v>12.35322</v>
       </c>
       <c r="N67">
-        <v>-2.281050000000002</v>
+        <v>-2.468220000000002</v>
       </c>
       <c r="O67">
-        <v>-0.4562100000000004</v>
+        <v>-0.4936440000000005</v>
       </c>
       <c r="P67">
-        <v>-1.824840000000002</v>
+        <v>-1.974576000000002</v>
       </c>
       <c r="Q67">
-        <v>1.415159999999998</v>
+        <v>1.265423999999998</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2998407656681226</v>
+        <v>0.3073125528936556</v>
       </c>
       <c r="T67">
-        <v>3.043342912631599</v>
+        <v>3.132852998297234</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.1625013870566042</v>
+        <v>0.1600392448284739</v>
       </c>
       <c r="W67">
-        <v>0.1229447963800905</v>
+        <v>0.12330623885918</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.812506935283021</v>
+        <v>0.8001962241423692</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1858683856309017</v>
+        <v>0.2258823078099927</v>
       </c>
       <c r="C68">
-        <v>8.970876433331625</v>
+        <v>-11.6088774357858</v>
       </c>
       <c r="D68">
-        <v>86.88087643333164</v>
+        <v>67.57612256421422</v>
       </c>
       <c r="E68">
-        <v>34.05</v>
+        <v>35.32500000000001</v>
       </c>
       <c r="F68">
-        <v>84.15000000000001</v>
+        <v>85.42500000000001</v>
       </c>
       <c r="G68">
         <v>6.24</v>
@@ -6863,45 +6863,45 @@
         <v>9.885</v>
       </c>
       <c r="M68">
-        <v>12.35322</v>
+        <v>17.15334</v>
       </c>
       <c r="N68">
-        <v>-2.468220000000002</v>
+        <v>-7.268340000000004</v>
       </c>
       <c r="O68">
-        <v>-0.4936440000000005</v>
+        <v>-1.453668000000001</v>
       </c>
       <c r="P68">
-        <v>-1.974576000000002</v>
+        <v>-5.814672000000003</v>
       </c>
       <c r="Q68">
-        <v>1.265423999999998</v>
+        <v>-2.574672000000003</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3073125528936556</v>
+        <v>0.3237945156452543</v>
       </c>
       <c r="T68">
-        <v>3.132852998297234</v>
+        <v>3.330302665063965</v>
       </c>
       <c r="U68">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1600392448284739</v>
+        <v>0.1152545218598827</v>
       </c>
       <c r="W68">
-        <v>0.12330623885918</v>
+        <v>0.1776568920105356</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y68">
-        <v>0.8001962241423692</v>
+        <v>0.5762726092994133</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2258823078099927</v>
+        <v>0.2274323078099927</v>
       </c>
       <c r="C69">
-        <v>-11.6088774357858</v>
+        <v>-13.46055342056766</v>
       </c>
       <c r="D69">
-        <v>67.57612256421422</v>
+        <v>66.99944657943234</v>
       </c>
       <c r="E69">
-        <v>35.32500000000001</v>
+        <v>36.6</v>
       </c>
       <c r="F69">
-        <v>85.42500000000001</v>
+        <v>86.7</v>
       </c>
       <c r="G69">
         <v>6.24</v>
@@ -6945,37 +6945,37 @@
         <v>9.885</v>
       </c>
       <c r="M69">
-        <v>17.15334</v>
+        <v>17.40936</v>
       </c>
       <c r="N69">
-        <v>-7.268340000000004</v>
+        <v>-7.52436</v>
       </c>
       <c r="O69">
-        <v>-1.453668000000001</v>
+        <v>-1.504872</v>
       </c>
       <c r="P69">
-        <v>-5.814672000000003</v>
+        <v>-6.019488</v>
       </c>
       <c r="Q69">
-        <v>-2.574672000000003</v>
+        <v>-2.779488</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3237945156452543</v>
+        <v>0.3324818442591685</v>
       </c>
       <c r="T69">
-        <v>3.330302665063965</v>
+        <v>3.434374623347214</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.1152545218598827</v>
+        <v>0.1135596024207668</v>
       </c>
       <c r="W69">
-        <v>0.1776568920105356</v>
+        <v>0.17799723183391</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5762726092994133</v>
+        <v>0.5677980121038337</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2274323078099927</v>
+        <v>0.2289823078099927</v>
       </c>
       <c r="C70">
-        <v>-13.46055342056766</v>
+        <v>-15.30247029938459</v>
       </c>
       <c r="D70">
-        <v>66.99944657943234</v>
+        <v>66.43252970061542</v>
       </c>
       <c r="E70">
-        <v>36.6</v>
+        <v>37.87500000000001</v>
       </c>
       <c r="F70">
-        <v>86.7</v>
+        <v>87.97500000000001</v>
       </c>
       <c r="G70">
         <v>6.24</v>
@@ -7027,37 +7027,37 @@
         <v>9.885</v>
       </c>
       <c r="M70">
-        <v>17.40936</v>
+        <v>17.66538</v>
       </c>
       <c r="N70">
-        <v>-7.52436</v>
+        <v>-7.780380000000003</v>
       </c>
       <c r="O70">
-        <v>-1.504872</v>
+        <v>-1.556076000000001</v>
       </c>
       <c r="P70">
-        <v>-6.019488</v>
+        <v>-6.224304000000002</v>
       </c>
       <c r="Q70">
-        <v>-2.779488</v>
+        <v>-2.984304000000002</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3324818442591685</v>
+        <v>0.3417296456868836</v>
       </c>
       <c r="T70">
-        <v>3.434374623347214</v>
+        <v>3.545160901519705</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1135596024207668</v>
+        <v>0.1119138110813353</v>
       </c>
       <c r="W70">
-        <v>0.17799723183391</v>
+        <v>0.1783277067348679</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5677980121038337</v>
+        <v>0.5595690554066767</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2289823078099927</v>
+        <v>0.2305323078099928</v>
       </c>
       <c r="C71">
-        <v>-15.30247029938459</v>
+        <v>-17.13487372413834</v>
       </c>
       <c r="D71">
-        <v>66.43252970061542</v>
+        <v>65.87512627586167</v>
       </c>
       <c r="E71">
-        <v>37.87500000000001</v>
+        <v>39.15000000000001</v>
       </c>
       <c r="F71">
-        <v>87.97500000000001</v>
+        <v>89.25000000000001</v>
       </c>
       <c r="G71">
         <v>6.24</v>
@@ -7109,37 +7109,37 @@
         <v>9.885</v>
       </c>
       <c r="M71">
-        <v>17.66538</v>
+        <v>17.9214</v>
       </c>
       <c r="N71">
-        <v>-7.780380000000003</v>
+        <v>-8.036400000000002</v>
       </c>
       <c r="O71">
-        <v>-1.556076000000001</v>
+        <v>-1.60728</v>
       </c>
       <c r="P71">
-        <v>-6.224304000000002</v>
+        <v>-6.429120000000002</v>
       </c>
       <c r="Q71">
-        <v>-2.984304000000002</v>
+        <v>-3.189120000000002</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3417296456868836</v>
+        <v>0.3515939672097798</v>
       </c>
       <c r="T71">
-        <v>3.545160901519705</v>
+        <v>3.663332931570362</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1119138110813353</v>
+        <v>0.110315042351602</v>
       </c>
       <c r="W71">
-        <v>0.1783277067348679</v>
+        <v>0.1786487394957983</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5595690554066767</v>
+        <v>0.5515752117580099</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2305323078099928</v>
+        <v>0.2320823078099927</v>
       </c>
       <c r="C72">
-        <v>-17.13487372413834</v>
+        <v>-18.95800117074337</v>
       </c>
       <c r="D72">
-        <v>65.87512627586167</v>
+        <v>65.32699882925664</v>
       </c>
       <c r="E72">
-        <v>39.15000000000001</v>
+        <v>40.425</v>
       </c>
       <c r="F72">
-        <v>89.25000000000001</v>
+        <v>90.52500000000001</v>
       </c>
       <c r="G72">
         <v>6.24</v>
@@ -7191,37 +7191,37 @@
         <v>9.885</v>
       </c>
       <c r="M72">
-        <v>17.9214</v>
+        <v>18.17742</v>
       </c>
       <c r="N72">
-        <v>-8.036400000000002</v>
+        <v>-8.292420000000002</v>
       </c>
       <c r="O72">
-        <v>-1.60728</v>
+        <v>-1.658484000000001</v>
       </c>
       <c r="P72">
-        <v>-6.429120000000002</v>
+        <v>-6.633936000000001</v>
       </c>
       <c r="Q72">
-        <v>-3.189120000000002</v>
+        <v>-3.393936000000001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3515939672097798</v>
+        <v>0.3621385867687377</v>
       </c>
       <c r="T72">
-        <v>3.663332931570362</v>
+        <v>3.789654756796926</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.110315042351602</v>
+        <v>0.1087613093607344</v>
       </c>
       <c r="W72">
-        <v>0.1786487394957983</v>
+        <v>0.1789607290803645</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5515752117580099</v>
+        <v>0.5438065468036717</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2320823078099928</v>
+        <v>0.2336323078099927</v>
       </c>
       <c r="C73">
-        <v>-18.95800117074337</v>
+        <v>-20.77208227646973</v>
       </c>
       <c r="D73">
-        <v>65.32699882925662</v>
+        <v>64.78791772353027</v>
       </c>
       <c r="E73">
-        <v>40.42499999999999</v>
+        <v>41.7</v>
       </c>
       <c r="F73">
-        <v>90.52499999999999</v>
+        <v>91.8</v>
       </c>
       <c r="G73">
         <v>6.24</v>
@@ -7273,37 +7273,37 @@
         <v>9.885</v>
       </c>
       <c r="M73">
-        <v>18.17742</v>
+        <v>18.43344</v>
       </c>
       <c r="N73">
-        <v>-8.292419999999998</v>
+        <v>-8.548440000000001</v>
       </c>
       <c r="O73">
-        <v>-1.658484</v>
+        <v>-1.709688</v>
       </c>
       <c r="P73">
-        <v>-6.633935999999999</v>
+        <v>-6.838752000000001</v>
       </c>
       <c r="Q73">
-        <v>-3.393935999999998</v>
+        <v>-3.598752000000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3621385867687377</v>
+        <v>0.3734363934390497</v>
       </c>
       <c r="T73">
-        <v>3.789654756796925</v>
+        <v>3.924999569539672</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1087613093607344</v>
+        <v>0.1072507356196131</v>
       </c>
       <c r="W73">
-        <v>0.1789607290803645</v>
+        <v>0.1792640522875817</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5438065468036719</v>
+        <v>0.5362536780980652</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2336323078099927</v>
+        <v>0.2351823078099928</v>
       </c>
       <c r="C74">
-        <v>-20.77208227646973</v>
+        <v>-22.57733916072013</v>
       </c>
       <c r="D74">
-        <v>64.78791772353027</v>
+        <v>64.25766083927988</v>
       </c>
       <c r="E74">
-        <v>41.7</v>
+        <v>42.975</v>
       </c>
       <c r="F74">
-        <v>91.8</v>
+        <v>93.075</v>
       </c>
       <c r="G74">
         <v>6.24</v>
@@ -7355,37 +7355,37 @@
         <v>9.885</v>
       </c>
       <c r="M74">
-        <v>18.43344</v>
+        <v>18.68946</v>
       </c>
       <c r="N74">
-        <v>-8.548440000000001</v>
+        <v>-8.804460000000001</v>
       </c>
       <c r="O74">
-        <v>-1.709688</v>
+        <v>-1.760892</v>
       </c>
       <c r="P74">
-        <v>-6.838752000000001</v>
+        <v>-7.043568</v>
       </c>
       <c r="Q74">
-        <v>-3.598752000000001</v>
+        <v>-3.803568</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3734363934390497</v>
+        <v>0.385571074677533</v>
       </c>
       <c r="T74">
-        <v>3.924999569539672</v>
+        <v>4.070369923967068</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1072507356196131</v>
+        <v>0.1057815474604403</v>
       </c>
       <c r="W74">
-        <v>0.1792640522875817</v>
+        <v>0.1795590652699436</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5362536780980652</v>
+        <v>0.5289077373022013</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2351823078099928</v>
+        <v>0.2367323078099928</v>
       </c>
       <c r="C75">
-        <v>-22.57733916072013</v>
+        <v>-24.37398673018228</v>
       </c>
       <c r="D75">
-        <v>64.25766083927988</v>
+        <v>63.73601326981772</v>
       </c>
       <c r="E75">
-        <v>42.975</v>
+        <v>44.24999999999999</v>
       </c>
       <c r="F75">
-        <v>93.075</v>
+        <v>94.34999999999999</v>
       </c>
       <c r="G75">
         <v>6.24</v>
@@ -7437,37 +7437,37 @@
         <v>9.885</v>
       </c>
       <c r="M75">
-        <v>18.68946</v>
+        <v>18.94548</v>
       </c>
       <c r="N75">
-        <v>-8.804460000000001</v>
+        <v>-9.06048</v>
       </c>
       <c r="O75">
-        <v>-1.760892</v>
+        <v>-1.812096</v>
       </c>
       <c r="P75">
-        <v>-7.043568</v>
+        <v>-7.248384</v>
       </c>
       <c r="Q75">
-        <v>-3.803568</v>
+        <v>-4.008384</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.385571074677533</v>
+        <v>0.3986391929343612</v>
       </c>
       <c r="T75">
-        <v>4.070369923967068</v>
+        <v>4.226922613350417</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1057815474604403</v>
+        <v>0.1043520670893532</v>
       </c>
       <c r="W75">
-        <v>0.1795590652699436</v>
+        <v>0.1798461049284579</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5289077373022013</v>
+        <v>0.5217603354467661</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2367323078099928</v>
+        <v>0.2382823078099927</v>
       </c>
       <c r="C76">
-        <v>-24.37398673018228</v>
+        <v>-26.16223296923785</v>
       </c>
       <c r="D76">
-        <v>63.73601326981772</v>
+        <v>63.22276703076216</v>
       </c>
       <c r="E76">
-        <v>44.24999999999999</v>
+        <v>45.525</v>
       </c>
       <c r="F76">
-        <v>94.34999999999999</v>
+        <v>95.625</v>
       </c>
       <c r="G76">
         <v>6.24</v>
@@ -7519,37 +7519,37 @@
         <v>9.885</v>
       </c>
       <c r="M76">
-        <v>18.94548</v>
+        <v>19.2015</v>
       </c>
       <c r="N76">
-        <v>-9.06048</v>
+        <v>-9.3165</v>
       </c>
       <c r="O76">
-        <v>-1.812096</v>
+        <v>-1.8633</v>
       </c>
       <c r="P76">
-        <v>-7.248384</v>
+        <v>-7.4532</v>
       </c>
       <c r="Q76">
-        <v>-4.008384</v>
+        <v>-4.2132</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3986391929343612</v>
+        <v>0.4127527606517357</v>
       </c>
       <c r="T76">
-        <v>4.226922613350417</v>
+        <v>4.395999517884433</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1043520670893532</v>
+        <v>0.1029607061948285</v>
       </c>
       <c r="W76">
-        <v>0.1798461049284579</v>
+        <v>0.1801254901960784</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5217603354467661</v>
+        <v>0.5148035309741427</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2382823078099927</v>
+        <v>0.2398323078099928</v>
       </c>
       <c r="C77">
-        <v>-26.16223296923785</v>
+        <v>-27.94227921645172</v>
       </c>
       <c r="D77">
-        <v>63.22276703076216</v>
+        <v>62.71772078354828</v>
       </c>
       <c r="E77">
-        <v>45.525</v>
+        <v>46.8</v>
       </c>
       <c r="F77">
-        <v>95.625</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="G77">
         <v>6.24</v>
@@ -7601,37 +7601,37 @@
         <v>9.885</v>
       </c>
       <c r="M77">
-        <v>19.2015</v>
+        <v>19.45752</v>
       </c>
       <c r="N77">
-        <v>-9.3165</v>
+        <v>-9.572520000000003</v>
       </c>
       <c r="O77">
-        <v>-1.8633</v>
+        <v>-1.914504000000001</v>
       </c>
       <c r="P77">
-        <v>-7.4532</v>
+        <v>-7.658016000000002</v>
       </c>
       <c r="Q77">
-        <v>-4.2132</v>
+        <v>-4.418016000000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.4127527606517357</v>
+        <v>0.4280424590122247</v>
       </c>
       <c r="T77">
-        <v>4.395999517884433</v>
+        <v>4.579166164462952</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.1029607061948285</v>
+        <v>0.101605960060686</v>
       </c>
       <c r="W77">
-        <v>0.1801254901960784</v>
+        <v>0.1803975232198143</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5148035309741427</v>
+        <v>0.5080298003034301</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2398323078099928</v>
+        <v>0.2413823078099928</v>
       </c>
       <c r="C78">
-        <v>-27.94227921645172</v>
+        <v>-29.71432042791416</v>
       </c>
       <c r="D78">
-        <v>62.71772078354828</v>
+        <v>62.22067957208584</v>
       </c>
       <c r="E78">
-        <v>46.8</v>
+        <v>48.075</v>
       </c>
       <c r="F78">
-        <v>96.90000000000001</v>
+        <v>98.175</v>
       </c>
       <c r="G78">
         <v>6.24</v>
@@ -7683,37 +7683,37 @@
         <v>9.885</v>
       </c>
       <c r="M78">
-        <v>19.45752</v>
+        <v>19.71354</v>
       </c>
       <c r="N78">
-        <v>-9.572520000000003</v>
+        <v>-9.828539999999998</v>
       </c>
       <c r="O78">
-        <v>-1.914504000000001</v>
+        <v>-1.965708</v>
       </c>
       <c r="P78">
-        <v>-7.658016000000002</v>
+        <v>-7.862831999999999</v>
       </c>
       <c r="Q78">
-        <v>-4.418016000000001</v>
+        <v>-4.622831999999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.4280424590122247</v>
+        <v>0.4446616963605823</v>
       </c>
       <c r="T78">
-        <v>4.579166164462952</v>
+        <v>4.778260345526558</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.101605960060686</v>
+        <v>0.10028640213782</v>
       </c>
       <c r="W78">
-        <v>0.1803975232198143</v>
+        <v>0.1806624904507257</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5080298003034301</v>
+        <v>0.5014320106891</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2413823078099928</v>
+        <v>0.2713717945184533</v>
       </c>
       <c r="C79">
-        <v>-29.71432042791416</v>
+        <v>-39.26148161279051</v>
       </c>
       <c r="D79">
-        <v>62.22067957208584</v>
+        <v>53.94851838720949</v>
       </c>
       <c r="E79">
-        <v>48.075</v>
+        <v>49.35</v>
       </c>
       <c r="F79">
-        <v>98.175</v>
+        <v>99.45</v>
       </c>
       <c r="G79">
         <v>6.24</v>
@@ -7765,45 +7765,45 @@
         <v>9.885</v>
       </c>
       <c r="M79">
-        <v>19.71354</v>
+        <v>23.45031</v>
       </c>
       <c r="N79">
-        <v>-9.828539999999998</v>
+        <v>-13.56531</v>
       </c>
       <c r="O79">
-        <v>-1.965708</v>
+        <v>-2.713062000000001</v>
       </c>
       <c r="P79">
-        <v>-7.862831999999999</v>
+        <v>-10.852248</v>
       </c>
       <c r="Q79">
-        <v>-4.622831999999999</v>
+        <v>-7.612248000000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4446616963605823</v>
+        <v>0.4679712585063384</v>
       </c>
       <c r="T79">
-        <v>4.778260345526558</v>
+        <v>5.057502893730444</v>
       </c>
       <c r="U79">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.10028640213782</v>
+        <v>0.08430592175540536</v>
       </c>
       <c r="W79">
-        <v>0.1806624904507257</v>
+        <v>0.2159206636500754</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y79">
-        <v>0.5014320106891</v>
+        <v>0.4215296087770268</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2713717945184533</v>
+        <v>0.2732717945184533</v>
       </c>
       <c r="C80">
-        <v>-39.26148161279051</v>
+        <v>-40.98709653475343</v>
       </c>
       <c r="D80">
-        <v>53.94851838720949</v>
+        <v>53.49790346524658</v>
       </c>
       <c r="E80">
-        <v>49.35</v>
+        <v>50.62500000000001</v>
       </c>
       <c r="F80">
-        <v>99.45</v>
+        <v>100.725</v>
       </c>
       <c r="G80">
         <v>6.24</v>
@@ -7847,37 +7847,37 @@
         <v>9.885</v>
       </c>
       <c r="M80">
-        <v>23.45031</v>
+        <v>23.750955</v>
       </c>
       <c r="N80">
-        <v>-13.56531</v>
+        <v>-13.865955</v>
       </c>
       <c r="O80">
-        <v>-2.713062000000001</v>
+        <v>-2.773191000000001</v>
       </c>
       <c r="P80">
-        <v>-10.852248</v>
+        <v>-11.092764</v>
       </c>
       <c r="Q80">
-        <v>-7.612248000000001</v>
+        <v>-7.852764000000004</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.4679712585063384</v>
+        <v>0.4880746517685451</v>
       </c>
       <c r="T80">
-        <v>5.057502893730444</v>
+        <v>5.298336364860466</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.08430592175540536</v>
+        <v>0.08323875818888123</v>
       </c>
       <c r="W80">
-        <v>0.2159206636500754</v>
+        <v>0.2161723008190618</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4215296087770268</v>
+        <v>0.4161937909444061</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2732717945184533</v>
+        <v>0.2751717945184533</v>
       </c>
       <c r="C81">
-        <v>-40.98709653475343</v>
+        <v>-42.70524612425446</v>
       </c>
       <c r="D81">
-        <v>53.49790346524658</v>
+        <v>53.05475387574554</v>
       </c>
       <c r="E81">
-        <v>50.62500000000001</v>
+        <v>51.9</v>
       </c>
       <c r="F81">
-        <v>100.725</v>
+        <v>102</v>
       </c>
       <c r="G81">
         <v>6.24</v>
@@ -7929,37 +7929,37 @@
         <v>9.885</v>
       </c>
       <c r="M81">
-        <v>23.750955</v>
+        <v>24.0516</v>
       </c>
       <c r="N81">
-        <v>-13.865955</v>
+        <v>-14.1666</v>
       </c>
       <c r="O81">
-        <v>-2.773191000000001</v>
+        <v>-2.833320000000001</v>
       </c>
       <c r="P81">
-        <v>-11.092764</v>
+        <v>-11.33328</v>
       </c>
       <c r="Q81">
-        <v>-7.852764000000004</v>
+        <v>-8.09328</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4880746517685451</v>
+        <v>0.5101883843569722</v>
       </c>
       <c r="T81">
-        <v>5.298336364860466</v>
+        <v>5.563253183103488</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.08323875818888123</v>
+        <v>0.08219827371152023</v>
       </c>
       <c r="W81">
-        <v>0.2161723008190618</v>
+        <v>0.2164176470588235</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4161937909444061</v>
+        <v>0.4109913685576011</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2751717945184533</v>
+        <v>0.2770717945184533</v>
       </c>
       <c r="C82">
-        <v>-42.70524612425446</v>
+        <v>-44.41611437430979</v>
       </c>
       <c r="D82">
-        <v>53.05475387574554</v>
+        <v>52.61888562569021</v>
       </c>
       <c r="E82">
-        <v>51.9</v>
+        <v>53.175</v>
       </c>
       <c r="F82">
-        <v>102</v>
+        <v>103.275</v>
       </c>
       <c r="G82">
         <v>6.24</v>
@@ -8011,37 +8011,37 @@
         <v>9.885</v>
       </c>
       <c r="M82">
-        <v>24.0516</v>
+        <v>24.352245</v>
       </c>
       <c r="N82">
-        <v>-14.1666</v>
+        <v>-14.467245</v>
       </c>
       <c r="O82">
-        <v>-2.833320000000001</v>
+        <v>-2.893449000000001</v>
       </c>
       <c r="P82">
-        <v>-11.33328</v>
+        <v>-11.573796</v>
       </c>
       <c r="Q82">
-        <v>-8.09328</v>
+        <v>-8.333796000000003</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.5101883843569722</v>
+        <v>0.5346298782704971</v>
       </c>
       <c r="T82">
-        <v>5.563253183103488</v>
+        <v>5.856055982214199</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.08219827371152023</v>
+        <v>0.08118348020890886</v>
       </c>
       <c r="W82">
-        <v>0.2164176470588235</v>
+        <v>0.2166569353667393</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4109913685576011</v>
+        <v>0.4059174010445443</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2770717945184533</v>
+        <v>0.2789717945184533</v>
       </c>
       <c r="C83">
-        <v>-44.41611437430979</v>
+        <v>-46.11987928086843</v>
       </c>
       <c r="D83">
-        <v>52.61888562569021</v>
+        <v>52.19012071913158</v>
       </c>
       <c r="E83">
-        <v>53.175</v>
+        <v>54.45000000000001</v>
       </c>
       <c r="F83">
-        <v>103.275</v>
+        <v>104.55</v>
       </c>
       <c r="G83">
         <v>6.24</v>
@@ -8093,37 +8093,37 @@
         <v>9.885</v>
       </c>
       <c r="M83">
-        <v>24.352245</v>
+        <v>24.65289</v>
       </c>
       <c r="N83">
-        <v>-14.467245</v>
+        <v>-14.76789</v>
       </c>
       <c r="O83">
-        <v>-2.893449000000001</v>
+        <v>-2.953578000000001</v>
       </c>
       <c r="P83">
-        <v>-11.573796</v>
+        <v>-11.814312</v>
       </c>
       <c r="Q83">
-        <v>-8.333796000000003</v>
+        <v>-8.574312000000003</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.5346298782704971</v>
+        <v>0.5617870937299693</v>
       </c>
       <c r="T83">
-        <v>5.856055982214199</v>
+        <v>6.181392425670545</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.08118348020890886</v>
+        <v>0.0801934377673368</v>
       </c>
       <c r="W83">
-        <v>0.2166569353667393</v>
+        <v>0.216890387374462</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4059174010445443</v>
+        <v>0.400967188836684</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2789717945184533</v>
+        <v>0.2808717945184533</v>
       </c>
       <c r="C84">
-        <v>-46.11987928086843</v>
+        <v>-47.81671308517269</v>
       </c>
       <c r="D84">
-        <v>52.19012071913158</v>
+        <v>51.76828691482731</v>
       </c>
       <c r="E84">
-        <v>54.45000000000001</v>
+        <v>55.725</v>
       </c>
       <c r="F84">
-        <v>104.55</v>
+        <v>105.825</v>
       </c>
       <c r="G84">
         <v>6.24</v>
@@ -8175,37 +8175,37 @@
         <v>9.885</v>
       </c>
       <c r="M84">
-        <v>24.65289</v>
+        <v>24.953535</v>
       </c>
       <c r="N84">
-        <v>-14.76789</v>
+        <v>-15.068535</v>
       </c>
       <c r="O84">
-        <v>-2.953578000000001</v>
+        <v>-3.013707000000001</v>
       </c>
       <c r="P84">
-        <v>-11.814312</v>
+        <v>-12.054828</v>
       </c>
       <c r="Q84">
-        <v>-8.574312000000003</v>
+        <v>-8.814828000000002</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.5617870937299693</v>
+        <v>0.5921392757140851</v>
       </c>
       <c r="T84">
-        <v>6.181392425670545</v>
+        <v>6.545003744827635</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.0801934377673368</v>
+        <v>0.07922725177013998</v>
       </c>
       <c r="W84">
-        <v>0.216890387374462</v>
+        <v>0.217118214032601</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.400967188836684</v>
+        <v>0.3961362588506999</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2808717945184533</v>
+        <v>0.2827717945184533</v>
       </c>
       <c r="C85">
-        <v>-47.81671308517269</v>
+        <v>-49.50678250445969</v>
       </c>
       <c r="D85">
-        <v>51.76828691482731</v>
+        <v>51.35321749554031</v>
       </c>
       <c r="E85">
-        <v>55.725</v>
+        <v>57.00000000000001</v>
       </c>
       <c r="F85">
-        <v>105.825</v>
+        <v>107.1</v>
       </c>
       <c r="G85">
         <v>6.24</v>
@@ -8257,37 +8257,37 @@
         <v>9.885</v>
       </c>
       <c r="M85">
-        <v>24.953535</v>
+        <v>25.25418</v>
       </c>
       <c r="N85">
-        <v>-15.068535</v>
+        <v>-15.36918</v>
       </c>
       <c r="O85">
-        <v>-3.013707000000001</v>
+        <v>-3.073836</v>
       </c>
       <c r="P85">
-        <v>-12.054828</v>
+        <v>-12.295344</v>
       </c>
       <c r="Q85">
-        <v>-8.814828000000002</v>
+        <v>-9.055344000000002</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.5921392757140851</v>
+        <v>0.6262854804462156</v>
       </c>
       <c r="T85">
-        <v>6.545003744827635</v>
+        <v>6.954066478879364</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.07922725177013998</v>
+        <v>0.07828407020144784</v>
       </c>
       <c r="W85">
-        <v>0.217118214032601</v>
+        <v>0.2173406162464986</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3961362588506999</v>
+        <v>0.3914203510072392</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2827717945184532</v>
+        <v>0.2846717945184533</v>
       </c>
       <c r="C86">
-        <v>-49.50678250445966</v>
+        <v>-51.1902489516525</v>
       </c>
       <c r="D86">
-        <v>51.35321749554033</v>
+        <v>50.9447510483475</v>
       </c>
       <c r="E86">
-        <v>56.99999999999999</v>
+        <v>58.275</v>
       </c>
       <c r="F86">
-        <v>107.1</v>
+        <v>108.375</v>
       </c>
       <c r="G86">
         <v>6.24</v>
@@ -8339,37 +8339,37 @@
         <v>9.885</v>
       </c>
       <c r="M86">
-        <v>25.25418</v>
+        <v>25.554825</v>
       </c>
       <c r="N86">
-        <v>-15.36918</v>
+        <v>-15.669825</v>
       </c>
       <c r="O86">
-        <v>-3.073836</v>
+        <v>-3.133965</v>
       </c>
       <c r="P86">
-        <v>-12.295344</v>
+        <v>-12.53586</v>
       </c>
       <c r="Q86">
-        <v>-9.055343999999998</v>
+        <v>-9.295860000000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.6262854804462151</v>
+        <v>0.6649845124759628</v>
       </c>
       <c r="T86">
-        <v>6.954066478879359</v>
+        <v>7.41767091080465</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.07828407020144784</v>
+        <v>0.07736308114025434</v>
       </c>
       <c r="W86">
-        <v>0.2173406162464986</v>
+        <v>0.217557785467128</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3914203510072393</v>
+        <v>0.3868154057012717</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2846717945184533</v>
+        <v>0.2865717945184533</v>
       </c>
       <c r="C87">
-        <v>-51.1902489516525</v>
+        <v>-52.86726874464964</v>
       </c>
       <c r="D87">
-        <v>50.9447510483475</v>
+        <v>50.54273125535035</v>
       </c>
       <c r="E87">
-        <v>58.275</v>
+        <v>59.54999999999999</v>
       </c>
       <c r="F87">
-        <v>108.375</v>
+        <v>109.65</v>
       </c>
       <c r="G87">
         <v>6.24</v>
@@ -8421,37 +8421,37 @@
         <v>9.885</v>
       </c>
       <c r="M87">
-        <v>25.554825</v>
+        <v>25.85547</v>
       </c>
       <c r="N87">
-        <v>-15.669825</v>
+        <v>-15.97047</v>
       </c>
       <c r="O87">
-        <v>-3.133965</v>
+        <v>-3.194094</v>
       </c>
       <c r="P87">
-        <v>-12.53586</v>
+        <v>-12.776376</v>
       </c>
       <c r="Q87">
-        <v>-9.295860000000001</v>
+        <v>-9.536376000000001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.6649845124759628</v>
+        <v>0.7092119776528173</v>
       </c>
       <c r="T87">
-        <v>7.41767091080465</v>
+        <v>7.947504547290696</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.07736308114025434</v>
+        <v>0.07646351042932115</v>
       </c>
       <c r="W87">
-        <v>0.217557785467128</v>
+        <v>0.2177699042407661</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3868154057012717</v>
+        <v>0.3823175521466057</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2865717945184533</v>
+        <v>0.2884717945184533</v>
       </c>
       <c r="C88">
-        <v>-52.86726874464964</v>
+        <v>-54.53799330578262</v>
       </c>
       <c r="D88">
-        <v>50.54273125535035</v>
+        <v>50.14700669421737</v>
       </c>
       <c r="E88">
-        <v>59.54999999999999</v>
+        <v>60.825</v>
       </c>
       <c r="F88">
-        <v>109.65</v>
+        <v>110.925</v>
       </c>
       <c r="G88">
         <v>6.24</v>
@@ -8503,37 +8503,37 @@
         <v>9.885</v>
       </c>
       <c r="M88">
-        <v>25.85547</v>
+        <v>26.156115</v>
       </c>
       <c r="N88">
-        <v>-15.97047</v>
+        <v>-16.271115</v>
       </c>
       <c r="O88">
-        <v>-3.194094</v>
+        <v>-3.254223000000001</v>
       </c>
       <c r="P88">
-        <v>-12.776376</v>
+        <v>-13.016892</v>
       </c>
       <c r="Q88">
-        <v>-9.536376000000001</v>
+        <v>-9.776892000000002</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.7092119776528173</v>
+        <v>0.7602436682414957</v>
       </c>
       <c r="T88">
-        <v>7.947504547290696</v>
+        <v>8.558851050928443</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.07646351042932115</v>
+        <v>0.07558461950484618</v>
       </c>
       <c r="W88">
-        <v>0.2177699042407661</v>
+        <v>0.2179771467207573</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3823175521466057</v>
+        <v>0.3779230975242309</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2884717945184533</v>
+        <v>0.2903717945184532</v>
       </c>
       <c r="C89">
-        <v>-54.53799330578262</v>
+        <v>-56.20256935197639</v>
       </c>
       <c r="D89">
-        <v>50.14700669421737</v>
+        <v>49.75743064802361</v>
       </c>
       <c r="E89">
-        <v>60.825</v>
+        <v>62.1</v>
       </c>
       <c r="F89">
-        <v>110.925</v>
+        <v>112.2</v>
       </c>
       <c r="G89">
         <v>6.24</v>
@@ -8585,37 +8585,37 @@
         <v>9.885</v>
       </c>
       <c r="M89">
-        <v>26.156115</v>
+        <v>26.45676</v>
       </c>
       <c r="N89">
-        <v>-16.271115</v>
+        <v>-16.57176</v>
       </c>
       <c r="O89">
-        <v>-3.254223000000001</v>
+        <v>-3.314352000000001</v>
       </c>
       <c r="P89">
-        <v>-13.016892</v>
+        <v>-13.257408</v>
       </c>
       <c r="Q89">
-        <v>-9.776892000000002</v>
+        <v>-10.017408</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.7602436682414957</v>
+        <v>0.8197806405949537</v>
       </c>
       <c r="T89">
-        <v>8.558851050928443</v>
+        <v>9.272088638505814</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.07558461950484618</v>
+        <v>0.07472570337410929</v>
       </c>
       <c r="W89">
-        <v>0.2179771467207573</v>
+        <v>0.218179679144385</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3779230975242309</v>
+        <v>0.3736285168705464</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2903717945184532</v>
+        <v>0.2922717945184533</v>
       </c>
       <c r="C90">
-        <v>-56.20256935197639</v>
+        <v>-57.86113907611442</v>
       </c>
       <c r="D90">
-        <v>49.75743064802361</v>
+        <v>49.37386092388559</v>
       </c>
       <c r="E90">
-        <v>62.1</v>
+        <v>63.37500000000001</v>
       </c>
       <c r="F90">
-        <v>112.2</v>
+        <v>113.475</v>
       </c>
       <c r="G90">
         <v>6.24</v>
@@ -8667,37 +8667,37 @@
         <v>9.885</v>
       </c>
       <c r="M90">
-        <v>26.45676</v>
+        <v>26.757405</v>
       </c>
       <c r="N90">
-        <v>-16.57176</v>
+        <v>-16.872405</v>
       </c>
       <c r="O90">
-        <v>-3.314352000000001</v>
+        <v>-3.374481</v>
       </c>
       <c r="P90">
-        <v>-13.257408</v>
+        <v>-13.497924</v>
       </c>
       <c r="Q90">
-        <v>-10.017408</v>
+        <v>-10.257924</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.8197806405949537</v>
+        <v>0.8901425170126768</v>
       </c>
       <c r="T90">
-        <v>9.272088638505814</v>
+        <v>10.11500578746089</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.07472570337410929</v>
+        <v>0.07388608872945639</v>
       </c>
       <c r="W90">
-        <v>0.218179679144385</v>
+        <v>0.2183776602775942</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3736285168705464</v>
+        <v>0.3694304436472819</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2922717945184533</v>
+        <v>0.2941717945184532</v>
       </c>
       <c r="C91">
-        <v>-57.86113907611442</v>
+        <v>-59.51384032007916</v>
       </c>
       <c r="D91">
-        <v>49.37386092388559</v>
+        <v>48.99615967992084</v>
       </c>
       <c r="E91">
-        <v>63.37500000000001</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="F91">
-        <v>113.475</v>
+        <v>114.75</v>
       </c>
       <c r="G91">
         <v>6.24</v>
@@ -8749,37 +8749,37 @@
         <v>9.885</v>
       </c>
       <c r="M91">
-        <v>26.757405</v>
+        <v>27.05805</v>
       </c>
       <c r="N91">
-        <v>-16.872405</v>
+        <v>-17.17305</v>
       </c>
       <c r="O91">
-        <v>-3.374481</v>
+        <v>-3.434610000000001</v>
       </c>
       <c r="P91">
-        <v>-13.497924</v>
+        <v>-13.73844</v>
       </c>
       <c r="Q91">
-        <v>-10.257924</v>
+        <v>-10.49844</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.8901425170126768</v>
+        <v>0.9745767687139445</v>
       </c>
       <c r="T91">
-        <v>10.11500578746089</v>
+        <v>11.12650636620698</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.07388608872945639</v>
+        <v>0.07306513218801798</v>
       </c>
       <c r="W91">
-        <v>0.2183776602775942</v>
+        <v>0.2185712418300653</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3694304436472819</v>
+        <v>0.3653256609400898</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2941717945184532</v>
+        <v>0.2960717945184533</v>
       </c>
       <c r="C92">
-        <v>-59.51384032007916</v>
+        <v>-61.16080673991074</v>
       </c>
       <c r="D92">
-        <v>48.99615967992084</v>
+        <v>48.62419326008926</v>
       </c>
       <c r="E92">
-        <v>64.65000000000001</v>
+        <v>65.92500000000001</v>
       </c>
       <c r="F92">
-        <v>114.75</v>
+        <v>116.025</v>
       </c>
       <c r="G92">
         <v>6.24</v>
@@ -8831,37 +8831,37 @@
         <v>9.885</v>
       </c>
       <c r="M92">
-        <v>27.05805</v>
+        <v>27.358695</v>
       </c>
       <c r="N92">
-        <v>-17.17305</v>
+        <v>-17.473695</v>
       </c>
       <c r="O92">
-        <v>-3.434610000000001</v>
+        <v>-3.494739</v>
       </c>
       <c r="P92">
-        <v>-13.73844</v>
+        <v>-13.978956</v>
       </c>
       <c r="Q92">
-        <v>-10.49844</v>
+        <v>-10.738956</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.9745767687139445</v>
+        <v>1.077774187459939</v>
       </c>
       <c r="T92">
-        <v>11.12650636620698</v>
+        <v>12.36278485134109</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.07306513218801798</v>
+        <v>0.07226221864749031</v>
       </c>
       <c r="W92">
-        <v>0.2185712418300653</v>
+        <v>0.2187605688429218</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3653256609400898</v>
+        <v>0.3613110932374516</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2960717945184533</v>
+        <v>0.2979717945184533</v>
       </c>
       <c r="C93">
-        <v>-61.16080673991074</v>
+        <v>-62.80216796349877</v>
       </c>
       <c r="D93">
-        <v>48.62419326008926</v>
+        <v>48.25783203650123</v>
       </c>
       <c r="E93">
-        <v>65.92500000000001</v>
+        <v>67.20000000000002</v>
       </c>
       <c r="F93">
-        <v>116.025</v>
+        <v>117.3</v>
       </c>
       <c r="G93">
         <v>6.24</v>
@@ -8913,37 +8913,37 @@
         <v>9.885</v>
       </c>
       <c r="M93">
-        <v>27.358695</v>
+        <v>27.65934</v>
       </c>
       <c r="N93">
-        <v>-17.473695</v>
+        <v>-17.77434</v>
       </c>
       <c r="O93">
-        <v>-3.494739</v>
+        <v>-3.554868000000001</v>
       </c>
       <c r="P93">
-        <v>-13.978956</v>
+        <v>-14.219472</v>
       </c>
       <c r="Q93">
-        <v>-10.738956</v>
+        <v>-10.979472</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.077774187459939</v>
+        <v>1.206770960892431</v>
       </c>
       <c r="T93">
-        <v>12.36278485134109</v>
+        <v>13.90813295775873</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.07226221864749031</v>
+        <v>0.07147675974914801</v>
       </c>
       <c r="W93">
-        <v>0.2187605688429218</v>
+        <v>0.2189457800511509</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3613110932374516</v>
+        <v>0.3573837987457401</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2979717945184533</v>
+        <v>0.2998717945184533</v>
       </c>
       <c r="C94">
-        <v>-62.80216796349877</v>
+        <v>-64.43804974119919</v>
       </c>
       <c r="D94">
-        <v>48.25783203650123</v>
+        <v>47.89695025880081</v>
       </c>
       <c r="E94">
-        <v>67.20000000000002</v>
+        <v>68.47499999999999</v>
       </c>
       <c r="F94">
-        <v>117.3</v>
+        <v>118.575</v>
       </c>
       <c r="G94">
         <v>6.24</v>
@@ -8995,37 +8995,37 @@
         <v>9.885</v>
       </c>
       <c r="M94">
-        <v>27.65934</v>
+        <v>27.959985</v>
       </c>
       <c r="N94">
-        <v>-17.77434</v>
+        <v>-18.07498500000001</v>
       </c>
       <c r="O94">
-        <v>-3.554868000000001</v>
+        <v>-3.614997000000001</v>
       </c>
       <c r="P94">
-        <v>-14.219472</v>
+        <v>-14.459988</v>
       </c>
       <c r="Q94">
-        <v>-10.979472</v>
+        <v>-11.219988</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.206770960892431</v>
+        <v>1.372623955305636</v>
       </c>
       <c r="T94">
-        <v>13.90813295775873</v>
+        <v>15.89500909458141</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.07147675974914801</v>
+        <v>0.0707081924400174</v>
       </c>
       <c r="W94">
-        <v>0.2189457800511509</v>
+        <v>0.2191270082226439</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3573837987457401</v>
+        <v>0.3535409622000869</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2998717945184533</v>
+        <v>0.3017717945184533</v>
       </c>
       <c r="C95">
-        <v>-64.43804974119919</v>
+        <v>-66.06857408974282</v>
       </c>
       <c r="D95">
-        <v>47.89695025880081</v>
+        <v>47.54142591025718</v>
       </c>
       <c r="E95">
-        <v>68.47499999999999</v>
+        <v>69.75</v>
       </c>
       <c r="F95">
-        <v>118.575</v>
+        <v>119.85</v>
       </c>
       <c r="G95">
         <v>6.24</v>
@@ -9077,37 +9077,37 @@
         <v>9.885</v>
       </c>
       <c r="M95">
-        <v>27.959985</v>
+        <v>28.26063</v>
       </c>
       <c r="N95">
-        <v>-18.07498500000001</v>
+        <v>-18.37563</v>
       </c>
       <c r="O95">
-        <v>-3.614997000000001</v>
+        <v>-3.675126000000001</v>
       </c>
       <c r="P95">
-        <v>-14.459988</v>
+        <v>-14.700504</v>
       </c>
       <c r="Q95">
-        <v>-11.219988</v>
+        <v>-11.460504</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.372623955305636</v>
+        <v>1.593761281189909</v>
       </c>
       <c r="T95">
-        <v>15.89500909458141</v>
+        <v>18.54417727701165</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.0707081924400174</v>
+        <v>0.06995597762682572</v>
       </c>
       <c r="W95">
-        <v>0.2191270082226439</v>
+        <v>0.2193043804755945</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3535409622000869</v>
+        <v>0.3497798881341286</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3017717945184533</v>
+        <v>0.3036717945184533</v>
       </c>
       <c r="C96">
-        <v>-66.06857408974282</v>
+        <v>-67.69385942978232</v>
       </c>
       <c r="D96">
-        <v>47.54142591025718</v>
+        <v>47.19114057021768</v>
       </c>
       <c r="E96">
-        <v>69.75</v>
+        <v>71.02500000000001</v>
       </c>
       <c r="F96">
-        <v>119.85</v>
+        <v>121.125</v>
       </c>
       <c r="G96">
         <v>6.24</v>
@@ -9159,37 +9159,37 @@
         <v>9.885</v>
       </c>
       <c r="M96">
-        <v>28.26063</v>
+        <v>28.56127500000001</v>
       </c>
       <c r="N96">
-        <v>-18.37563</v>
+        <v>-18.676275</v>
       </c>
       <c r="O96">
-        <v>-3.675126000000001</v>
+        <v>-3.735255000000001</v>
       </c>
       <c r="P96">
-        <v>-14.700504</v>
+        <v>-14.94102</v>
       </c>
       <c r="Q96">
-        <v>-11.460504</v>
+        <v>-11.70102</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.593761281189909</v>
+        <v>1.903353537427892</v>
       </c>
       <c r="T96">
-        <v>18.54417727701165</v>
+        <v>22.25301273241399</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.06995597762682572</v>
+        <v>0.06921959891496439</v>
       </c>
       <c r="W96">
-        <v>0.2193043804755945</v>
+        <v>0.2194780185758514</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3497798881341286</v>
+        <v>0.346097994574822</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3036717945184533</v>
+        <v>0.3055717945184533</v>
       </c>
       <c r="C97">
-        <v>-67.69385942978232</v>
+        <v>-69.31402071740257</v>
       </c>
       <c r="D97">
-        <v>47.19114057021768</v>
+        <v>46.84597928259743</v>
       </c>
       <c r="E97">
-        <v>71.02500000000001</v>
+        <v>72.30000000000001</v>
       </c>
       <c r="F97">
-        <v>121.125</v>
+        <v>122.4</v>
       </c>
       <c r="G97">
         <v>6.24</v>
@@ -9241,37 +9241,37 @@
         <v>9.885</v>
       </c>
       <c r="M97">
-        <v>28.56127500000001</v>
+        <v>28.86192</v>
       </c>
       <c r="N97">
-        <v>-18.676275</v>
+        <v>-18.97692</v>
       </c>
       <c r="O97">
-        <v>-3.735255000000001</v>
+        <v>-3.795384</v>
       </c>
       <c r="P97">
-        <v>-14.94102</v>
+        <v>-15.181536</v>
       </c>
       <c r="Q97">
-        <v>-11.70102</v>
+        <v>-11.941536</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.903353537427892</v>
+        <v>2.367741921784865</v>
       </c>
       <c r="T97">
-        <v>22.25301273241399</v>
+        <v>27.81626591551749</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.06921959891496439</v>
+        <v>0.06849856142626685</v>
       </c>
       <c r="W97">
-        <v>0.2194780185758514</v>
+        <v>0.2196480392156863</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.346097994574822</v>
+        <v>0.3424928071313343</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3055717945184533</v>
+        <v>0.3074717945184532</v>
       </c>
       <c r="C98">
-        <v>-69.31402071740256</v>
+        <v>-70.92916956990204</v>
       </c>
       <c r="D98">
-        <v>46.84597928259743</v>
+        <v>46.50583043009795</v>
       </c>
       <c r="E98">
-        <v>72.29999999999998</v>
+        <v>73.57499999999999</v>
       </c>
       <c r="F98">
-        <v>122.4</v>
+        <v>123.675</v>
       </c>
       <c r="G98">
         <v>6.24</v>
@@ -9323,37 +9323,37 @@
         <v>9.885</v>
       </c>
       <c r="M98">
-        <v>28.86192</v>
+        <v>29.162565</v>
       </c>
       <c r="N98">
-        <v>-18.97692</v>
+        <v>-19.277565</v>
       </c>
       <c r="O98">
-        <v>-3.795384</v>
+        <v>-3.855513000000001</v>
       </c>
       <c r="P98">
-        <v>-15.181536</v>
+        <v>-15.422052</v>
       </c>
       <c r="Q98">
-        <v>-11.941536</v>
+        <v>-12.182052</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.367741921784859</v>
+        <v>3.141722562379812</v>
       </c>
       <c r="T98">
-        <v>27.81626591551742</v>
+        <v>37.08835455402322</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.06849856142626687</v>
+        <v>0.06779239068991359</v>
       </c>
       <c r="W98">
-        <v>0.2196480392156863</v>
+        <v>0.2198145542753184</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3424928071313342</v>
+        <v>0.3389619534495679</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3074717945184532</v>
+        <v>0.3093717945184533</v>
       </c>
       <c r="C99">
-        <v>-70.92916956990204</v>
+        <v>-72.5394143861337</v>
       </c>
       <c r="D99">
-        <v>46.50583043009795</v>
+        <v>46.17058561386629</v>
       </c>
       <c r="E99">
-        <v>73.57499999999999</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="F99">
-        <v>123.675</v>
+        <v>124.95</v>
       </c>
       <c r="G99">
         <v>6.24</v>
@@ -9405,37 +9405,37 @@
         <v>9.885</v>
       </c>
       <c r="M99">
-        <v>29.162565</v>
+        <v>29.46321</v>
       </c>
       <c r="N99">
-        <v>-19.277565</v>
+        <v>-19.57821</v>
       </c>
       <c r="O99">
-        <v>-3.855513000000001</v>
+        <v>-3.915642</v>
       </c>
       <c r="P99">
-        <v>-15.422052</v>
+        <v>-15.662568</v>
       </c>
       <c r="Q99">
-        <v>-12.182052</v>
+        <v>-12.422568</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.141722562379812</v>
+        <v>4.689683843569718</v>
       </c>
       <c r="T99">
-        <v>37.08835455402322</v>
+        <v>55.63253183103483</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.06779239068991359</v>
+        <v>0.06710063160124101</v>
       </c>
       <c r="W99">
-        <v>0.2198145542753184</v>
+        <v>0.2199776710684274</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3389619534495679</v>
+        <v>0.3355031580062051</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3093717945184533</v>
+        <v>0.3112717945184533</v>
       </c>
       <c r="C100">
-        <v>-72.5394143861337</v>
+        <v>-74.14486046167808</v>
       </c>
       <c r="D100">
-        <v>46.17058561386629</v>
+        <v>45.84013953832191</v>
       </c>
       <c r="E100">
-        <v>74.84999999999999</v>
+        <v>76.125</v>
       </c>
       <c r="F100">
-        <v>124.95</v>
+        <v>126.225</v>
       </c>
       <c r="G100">
         <v>6.24</v>
@@ -9487,37 +9487,37 @@
         <v>9.885</v>
       </c>
       <c r="M100">
-        <v>29.46321</v>
+        <v>29.763855</v>
       </c>
       <c r="N100">
-        <v>-19.57821</v>
+        <v>-19.878855</v>
       </c>
       <c r="O100">
-        <v>-3.915642</v>
+        <v>-3.975771</v>
       </c>
       <c r="P100">
-        <v>-15.662568</v>
+        <v>-15.903084</v>
       </c>
       <c r="Q100">
-        <v>-12.422568</v>
+        <v>-12.663084</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.689683843569718</v>
+        <v>9.333567687139436</v>
       </c>
       <c r="T100">
-        <v>55.63253183103483</v>
+        <v>111.2650636620697</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.06710063160124101</v>
+        <v>0.06642284744365272</v>
       </c>
       <c r="W100">
-        <v>0.2199776710684274</v>
+        <v>0.2201374925727867</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3355031580062051</v>
+        <v>0.3321142372182635</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3112717945184533</v>
-      </c>
-      <c r="C101">
-        <v>-74.14486046167808</v>
-      </c>
-      <c r="D101">
-        <v>45.84013953832191</v>
-      </c>
-      <c r="E101">
-        <v>76.125</v>
-      </c>
-      <c r="F101">
-        <v>126.225</v>
-      </c>
-      <c r="G101">
-        <v>6.24</v>
-      </c>
-      <c r="H101">
-        <v>77.40000000000001</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>13.125</v>
-      </c>
-      <c r="K101">
-        <v>3.24</v>
-      </c>
-      <c r="L101">
-        <v>9.885</v>
-      </c>
-      <c r="M101">
-        <v>29.763855</v>
-      </c>
-      <c r="N101">
-        <v>-19.878855</v>
-      </c>
-      <c r="O101">
-        <v>-3.975771</v>
-      </c>
-      <c r="P101">
-        <v>-15.903084</v>
-      </c>
-      <c r="Q101">
-        <v>-12.663084</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>9.333567687139436</v>
-      </c>
-      <c r="T101">
-        <v>111.2650636620697</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06642284744365272</v>
-      </c>
-      <c r="W101">
-        <v>0.2201374925727867</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3321142372182635</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
